--- a/examples/validation_results/validation_frame_moment_release.xlsx
+++ b/examples/validation_results/validation_frame_moment_release.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Node Displacements" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Maximum Displacement Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Reaction Forces" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Member Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Member Full Results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Frame Member Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Frame Member Full Results" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0128097137669131</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.00429138568796626</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009334393834214193</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005875642721208698</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01353409407178715</v>
+        <v>3.761445368295371</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.012844443226954</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.004291377357561463</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.000755565984787582</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009331687918622317</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0005888482869970602</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01356342587227887</v>
+        <v>3.726938275138332</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01290339526324743</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005039316492279876</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0007558585541508834</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.001070169352779969</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.006773559198856145</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00057958013234802</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01387312661885717</v>
+        <v>3.728194767154632</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0129205791234349</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005042666858051312</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0008163740889860875</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.001296178924107323</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.00752700330388983</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0005839113268276019</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01389375113421133</v>
+        <v>3.763925524839729</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.08422531326366116</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01382352321936229</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.001609558593798498</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001091937175770063</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="J10" t="n">
-        <v>0.004967274058364416</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08536734661113098</v>
+        <v>8.67544527906699</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1297075743306731</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.01382244404254099</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.001491771440511998</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="H11" t="n">
-        <v>0.001093009262885102</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="J11" t="n">
-        <v>0.005274182961996149</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="K11" t="n">
-        <v>0.130450527711033</v>
+        <v>10.05164900906162</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1292765635896758</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02019608507901711</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001493673526759431</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1308531344931367</v>
+        <v>10.07036846435135</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.08374209521178606</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02019522961700954</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001607656507551068</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.002179807909866056</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.000889993047089781</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="J13" t="n">
-        <v>0.004663764944930242</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0861578224492115</v>
+        <v>8.696320729036229</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4746865315037455</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.02091067317803995</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.002300039659772865</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0005792017214737926</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="J14" t="n">
-        <v>0.007070915224504301</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4751524488269546</v>
+        <v>12.1308975563951</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5353453752792312</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.02091067828346176</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.002175173928523727</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0005791054802541305</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="J15" t="n">
-        <v>0.007070520459421152</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="K15" t="n">
-        <v>0.535758022507134</v>
+        <v>14.63546035427502</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5354068589467963</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03157201090228527</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002175859458574943</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0007408499310935353</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.192528065686288</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5363413379966829</v>
+        <v>14.66963584676064</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4747587126453503</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="F17" t="n">
-        <v>0.03157116725401265</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002299354129721651</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0008078657293793546</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1919280290521911</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="J17" t="n">
-        <v>0.007069048702360571</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4758128422645452</v>
+        <v>12.17136814323758</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8693932027947637</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.02354482424360938</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.002406814221431988</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0001818926669167243</v>
+        <v>-0.009077683545820888</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05018136607334805</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="J18" t="n">
-        <v>0.007409214359710549</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8697152939721688</v>
+        <v>13.78483278652767</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.929500914833618</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.02354482403202064</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.002279723241984587</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0001819140044221856</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.05021271910715217</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="J19" t="n">
-        <v>0.007409200793266503</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9298018641373503</v>
+        <v>16.31694146645215</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9298249044510045</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03489745300852468</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="G20" t="n">
-        <v>0.002280221647465502</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0002293826508512665</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="I20" t="n">
-        <v>0.009055914509505684</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00740935996088564</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9304823397435136</v>
+        <v>16.35298361114208</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8697155083131587</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03489758572708599</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002406315815951078</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0002052034834714622</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="I21" t="n">
-        <v>0.008780674266115432</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="J21" t="n">
-        <v>0.007409370087792433</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8704186907723209</v>
+        <v>13.82743303219325</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9304823397435136</v>
+        <v>16.35298361114208</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9298249044510045</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03489745300852468</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002280221647465502</v>
+        <v>-0.01193004232021133</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.9298249044510045</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9298249044510045</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03489745300852468</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002280221647465502</v>
+        <v>-0.01193004232021133</v>
       </c>
     </row>
     <row r="4">
@@ -1289,16 +1289,16 @@
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03489758572708599</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8697155083131587</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03489758572708599</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002406315815951078</v>
+        <v>-0.01708286628405483</v>
       </c>
     </row>
     <row r="5">
@@ -1311,16 +1311,16 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.002406814221431988</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8693932027947637</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02354482424360938</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002406814221431988</v>
+        <v>0.01709782427089189</v>
       </c>
     </row>
   </sheetData>
@@ -1345,32 +1345,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fx ()</t>
+          <t>Fx (KN)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Fy ()</t>
+          <t>Fy (KN)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fz ()</t>
+          <t>Fz (KN)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mx (·)</t>
+          <t>Mx (KN*M)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>My (·)</t>
+          <t>My (KN*M)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mz (·)</t>
+          <t>Mz (KN*M)</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>3.119530228461257</v>
+        <v>-475.6982651531055</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3677966592998273</v>
+        <v>-13.20417079465767</v>
       </c>
       <c r="D2" t="n">
-        <v>129.0333320192032</v>
+        <v>-1380.213673753829</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.794135121631332</v>
+        <v>66.4774354336206</v>
       </c>
       <c r="F2" t="n">
-        <v>9.398789852761077</v>
+        <v>-1878.351598355772</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.001672298312959399</v>
+        <v>0.01454786787215924</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1.092972341477125</v>
+        <v>-418.6737544032946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3679948422204428</v>
+        <v>-13.18917439722999</v>
       </c>
       <c r="D3" t="n">
-        <v>119.379425596438</v>
+        <v>-977.1609122504613</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.79452943263938</v>
+        <v>66.42140103278049</v>
       </c>
       <c r="F3" t="n">
-        <v>5.354240678936237</v>
+        <v>-1755.785178255167</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.001675952816837787</v>
+        <v>0.0998835270571985</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.829596308885847</v>
+        <v>-554.9044043380102</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.451106080371859</v>
+        <v>16.26814280349655</v>
       </c>
       <c r="D4" t="n">
-        <v>-119.4256515558396</v>
+        <v>979.0184522729362</v>
       </c>
       <c r="E4" t="n">
-        <v>2.145243562172753</v>
+        <v>-79.99422900793247</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4763551195039941</v>
+        <v>-1953.2035400049</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001649574222836672</v>
+        <v>-0.07155857263245415</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-2.382906261097865</v>
+        <v>-550.7235761049859</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2846854211465715</v>
+        <v>10.12520238831702</v>
       </c>
       <c r="D5" t="n">
-        <v>-128.9871060598018</v>
+        <v>1378.356133731357</v>
       </c>
       <c r="E5" t="n">
-        <v>1.813228667279133</v>
+        <v>-67.76492763695965</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.578736338415123</v>
+        <v>-1953.662995332046</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001661901468663174</v>
+        <v>0.1850957102150153</v>
       </c>
     </row>
   </sheetData>
@@ -1477,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,12 +1518,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>N_tension (+) (KN)</t>
+          <t>N (KN)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sigma (KN/M^2)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_i (KN)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_i (KN)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_i (KN)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>My_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_j (KN)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_j (KN)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_j (KN)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_j (KN*M)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>My_j (KN*M)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_j (KN*M)</t>
         </is>
       </c>
     </row>
@@ -1546,16 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0001361111097248978</v>
+        <v>0.001455921596786739</v>
       </c>
       <c r="H2" t="n">
-        <v>-129.0333320192031</v>
+        <v>1380.213673753829</v>
       </c>
       <c r="I2" t="n">
-        <v>-27222.22194497956</v>
+        <v>291184.3193573478</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-1380.213673753829</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-13.20417079465767</v>
+      </c>
+      <c r="L2" t="n">
+        <v>475.6982651531055</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01454786787215924</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-1878.351598355772</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-66.4774354336206</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1380.213673753829</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13.20417079465767</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-475.6982651531055</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.01454786787215924</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-975.8379925628601</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-12.74758933432537</v>
       </c>
     </row>
     <row r="3">
@@ -1577,16 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.000755565984787582</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001259276641312637</v>
+        <v>0.001030760455960402</v>
       </c>
       <c r="H3" t="n">
-        <v>-119.379425596438</v>
+        <v>977.1609122504611</v>
       </c>
       <c r="I3" t="n">
-        <v>-25185.53282625273</v>
+        <v>206152.0911920804</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-977.1609122504613</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-13.18917439722999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>418.6737544032946</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0998835270571985</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-1755.785178255167</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-66.42140103278049</v>
+      </c>
+      <c r="P3" t="n">
+        <v>977.1609122504613</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>13.18917439722999</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-418.6737544032946</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.0998835270571985</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-756.2573481646002</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-12.71364535059946</v>
       </c>
     </row>
     <row r="4">
@@ -1608,16 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007558585541508834</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001259764256918139</v>
+        <v>-0.001032719886363857</v>
       </c>
       <c r="H4" t="n">
-        <v>119.4256515558396</v>
+        <v>-979.018452272936</v>
       </c>
       <c r="I4" t="n">
-        <v>25195.28513836278</v>
+        <v>-206543.9772727713</v>
+      </c>
+      <c r="J4" t="n">
+        <v>979.0184522729362</v>
+      </c>
+      <c r="K4" t="n">
+        <v>16.26814280349655</v>
+      </c>
+      <c r="L4" t="n">
+        <v>554.9044043380102</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.07155857263245415</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1953.2035400049</v>
+      </c>
+      <c r="O4" t="n">
+        <v>79.99422900793247</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-979.0184522729362</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-16.26814280349655</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-404.9044043380101</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.07155857263245415</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-926.2228860231605</v>
+      </c>
+      <c r="U4" t="n">
+        <v>17.61462781304681</v>
       </c>
     </row>
     <row r="5">
@@ -1639,16 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008163740889860875</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001360623481643479</v>
+        <v>-0.001453962166383287</v>
       </c>
       <c r="H5" t="n">
-        <v>128.9871060598018</v>
+        <v>-1378.356133731356</v>
       </c>
       <c r="I5" t="n">
-        <v>27212.46963286958</v>
+        <v>-290792.4332766574</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1378.356133731357</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10.12520238831702</v>
+      </c>
+      <c r="L5" t="n">
+        <v>550.7235761049859</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1850957102150153</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1953.662995332046</v>
+      </c>
+      <c r="O5" t="n">
+        <v>67.76492763695965</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1378.356133731357</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-10.12520238831702</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-400.7235761049859</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.1850957102150153</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-900.678461297869</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-7.013713307057571</v>
       </c>
     </row>
     <row r="6">
@@ -1670,16 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0007928919354491112</v>
+        <v>0.005343562120812355</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0001321486559081852</v>
+        <v>0.0008905936868020591</v>
       </c>
       <c r="H6" t="n">
-        <v>-125.2769258009596</v>
+        <v>844.282815088352</v>
       </c>
       <c r="I6" t="n">
-        <v>-26429.73118163703</v>
+        <v>178118.7373604118</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-844.2828150883522</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-33.46616407719057</v>
+      </c>
+      <c r="L6" t="n">
+        <v>370.7493797662693</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4268812346987415</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1047.763457591656</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-107.251505406429</v>
+      </c>
+      <c r="P6" t="n">
+        <v>844.2828150883522</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>33.46616407719057</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-370.7493797662693</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.4268812346987415</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1176.73282100596</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-93.54547905671429</v>
       </c>
     </row>
     <row r="7">
@@ -1701,16 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0007362054557244158</v>
+        <v>0.003041978811124054</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0001227009092874026</v>
+        <v>0.0005069964685206757</v>
       </c>
       <c r="H7" t="n">
-        <v>-116.3204620044577</v>
+        <v>480.6326521576005</v>
       </c>
       <c r="I7" t="n">
-        <v>-24540.18185748053</v>
+        <v>101399.2937041351</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-480.6326521576007</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-33.45060406740529</v>
+      </c>
+      <c r="L7" t="n">
+        <v>418.9725901611122</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3991908776797221</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1395.756269664567</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-107.2509664857333</v>
+      </c>
+      <c r="P7" t="n">
+        <v>480.6326521576007</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>33.45060406740529</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-418.9725901611122</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.3991908776797221</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1118.079271302104</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-93.45265791869829</v>
       </c>
     </row>
     <row r="8">
@@ -1732,16 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0007378149726085477</v>
+        <v>-0.003106655500755174</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001229691621014246</v>
+        <v>-0.000517775916792529</v>
       </c>
       <c r="H8" t="n">
-        <v>116.5747656721505</v>
+        <v>-490.8515691193175</v>
       </c>
       <c r="I8" t="n">
-        <v>24593.83242028492</v>
+        <v>-103555.1833585058</v>
+      </c>
+      <c r="J8" t="n">
+        <v>490.8515691193177</v>
+      </c>
+      <c r="K8" t="n">
+        <v>118.6258911179426</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1194.292273501664</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.07155857263245415</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-2994.386493514121</v>
+      </c>
+      <c r="O8" t="n">
+        <v>324.687872756385</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-490.8515691193177</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-118.6258911179426</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1044.292273501664</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.07155857263245415</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-3721.36714749586</v>
+      </c>
+      <c r="U8" t="n">
+        <v>387.0674739512706</v>
       </c>
     </row>
     <row r="9">
@@ -1763,16 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0007912824185649803</v>
+        <v>-0.005278885431181244</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001318804030941634</v>
+        <v>-0.0008798142385302073</v>
       </c>
       <c r="H9" t="n">
-        <v>125.0226221332669</v>
+        <v>-834.0638981266366</v>
       </c>
       <c r="I9" t="n">
-        <v>26376.08061883268</v>
+        <v>-175962.8477060414</v>
+      </c>
+      <c r="J9" t="n">
+        <v>834.0638981266368</v>
+      </c>
+      <c r="K9" t="n">
+        <v>45.05774551440441</v>
+      </c>
+      <c r="L9" t="n">
+        <v>446.3275434442011</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4551684177415671</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1123.453614995791</v>
+      </c>
+      <c r="O9" t="n">
+        <v>165.0996718042885</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-834.0638981266368</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-45.05774551440441</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-296.3275434442011</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.4551684177415671</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1104.511645669415</v>
+      </c>
+      <c r="U9" t="n">
+        <v>105.246801282138</v>
       </c>
     </row>
     <row r="10">
@@ -1794,16 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.000690481065974367</v>
+        <v>0.002374012492255152</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0001150801776623945</v>
+        <v>0.0003956687487091919</v>
       </c>
       <c r="H10" t="n">
-        <v>-109.09600842395</v>
+        <v>375.0939737763139</v>
       </c>
       <c r="I10" t="n">
-        <v>-23016.0355324789</v>
+        <v>79133.74974183837</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-375.0939737763142</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-23.50754841617129</v>
+      </c>
+      <c r="L10" t="n">
+        <v>237.2786231035455</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3455385960838586</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-550.1129580527219</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-56.50944714402618</v>
+      </c>
+      <c r="P10" t="n">
+        <v>375.0939737763142</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>23.50754841617129</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-237.2786231035455</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.3455385960838586</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-873.5587805685493</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-84.53584335300144</v>
       </c>
     </row>
     <row r="11">
@@ -1825,16 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0006834024880117287</v>
+        <v>0.002145286274060163</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0001139004146686215</v>
+        <v>0.0003575477123433605</v>
       </c>
       <c r="H11" t="n">
-        <v>-107.9775931058531</v>
+        <v>338.9552313015058</v>
       </c>
       <c r="I11" t="n">
-        <v>-22780.08293372429</v>
+        <v>71509.54246867209</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-338.9552313015058</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-23.4738521565387</v>
+      </c>
+      <c r="L11" t="n">
+        <v>232.360609862576</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3731922717374728</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-315.6461386515213</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-56.36346879001178</v>
+      </c>
+      <c r="P11" t="n">
+        <v>338.9552313015058</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23.4738521565387</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-232.360609862576</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.3731922717374728</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1078.517520523936</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-84.47964414922058</v>
       </c>
     </row>
     <row r="12">
@@ -1856,16 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0006821859318155122</v>
+        <v>-0.002092006254182372</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001136976553025854</v>
+        <v>-0.0003486677090303953</v>
       </c>
       <c r="H12" t="n">
-        <v>107.7853772268509</v>
+        <v>-330.5369881608148</v>
       </c>
       <c r="I12" t="n">
-        <v>22739.53106051707</v>
+        <v>-69733.54180607905</v>
+      </c>
+      <c r="J12" t="n">
+        <v>330.5369881608146</v>
+      </c>
+      <c r="K12" t="n">
+        <v>98.68818091821899</v>
+      </c>
+      <c r="L12" t="n">
+        <v>967.6109033612859</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.7017888395369127</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-2988.329852586897</v>
+      </c>
+      <c r="O12" t="n">
+        <v>320.6255905894019</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-330.5369881608146</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-98.68818091821899</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-817.6109033612859</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.7017888395369127</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-2367.335567580818</v>
+      </c>
+      <c r="U12" t="n">
+        <v>271.503494919912</v>
       </c>
     </row>
     <row r="13">
@@ -1887,16 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0006916976221705835</v>
+        <v>-0.002427292512132957</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001152829370284306</v>
+        <v>-0.0004045487520221595</v>
       </c>
       <c r="H13" t="n">
-        <v>109.2882243029522</v>
+        <v>-383.5122169170072</v>
       </c>
       <c r="I13" t="n">
-        <v>23056.58740568612</v>
+        <v>-80909.75040443189</v>
+      </c>
+      <c r="J13" t="n">
+        <v>383.5122169170072</v>
+      </c>
+      <c r="K13" t="n">
+        <v>28.44961730178392</v>
+      </c>
+      <c r="L13" t="n">
+        <v>309.8323268183962</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3176639268975212</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-621.8472626633337</v>
+      </c>
+      <c r="O13" t="n">
+        <v>45.52697080804194</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-383.5122169170072</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-28.44961730178392</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-159.8323268183962</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.3176639268975212</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-787.1466982470427</v>
+      </c>
+      <c r="U13" t="n">
+        <v>125.1707330026616</v>
       </c>
     </row>
     <row r="14">
@@ -1918,16 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0001067745616591229</v>
+        <v>0.0006447200771039496</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.779576027652048e-05</v>
+        <v>0.0001074533461839916</v>
       </c>
       <c r="H14" t="n">
-        <v>-16.87038074214141</v>
+        <v>101.865772182424</v>
       </c>
       <c r="I14" t="n">
-        <v>-3559.152055304095</v>
+        <v>21490.66923679832</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-101.8657721824238</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-5.043036174986128</v>
+      </c>
+      <c r="L14" t="n">
+        <v>86.80693093240026</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05581601372114864</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-130.2789316849898</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-2.14185622884861</v>
+      </c>
+      <c r="P14" t="n">
+        <v>101.8657721824238</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.043036174986128</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-86.80693093240026</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.05581601372114864</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-390.5626539094091</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-28.11636082106827</v>
       </c>
     </row>
     <row r="15">
@@ -1949,16 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0001045493134608608</v>
+        <v>0.0005432565124276027</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.742488557681013e-05</v>
+        <v>9.054275207126712e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>-16.51879152681601</v>
+        <v>85.83452896356123</v>
       </c>
       <c r="I15" t="n">
-        <v>-3484.977115362026</v>
+        <v>18108.55041425342</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-85.8345289635613</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-5.049790589544841</v>
+      </c>
+      <c r="L15" t="n">
+        <v>68.77545927978912</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05592852579814611</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-36.84432557254138</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-2.174876591812904</v>
+      </c>
+      <c r="P15" t="n">
+        <v>85.8345289635613</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.049790589544841</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-68.77545927978912</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.05592852579814611</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-375.8084301061951</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-28.12386694545614</v>
       </c>
     </row>
     <row r="16">
@@ -1980,16 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001043621888905583</v>
+        <v>-0.0005350612470906464</v>
       </c>
       <c r="G16" t="n">
-        <v>1.739369814842639e-05</v>
+        <v>-8.917687451510774e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>16.48922584470822</v>
+        <v>-84.53967704032213</v>
       </c>
       <c r="I16" t="n">
-        <v>3478.739629685278</v>
+        <v>-17835.37490302155</v>
+      </c>
+      <c r="J16" t="n">
+        <v>84.5396770403222</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5.976631614420171</v>
+      </c>
+      <c r="L16" t="n">
+        <v>171.1038425458343</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.05544883212311946</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-209.6149089029861</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.765111141116449</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-84.5396770403222</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-5.976631614420171</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-21.10384254583424</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.05544883212311946</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-367.0081463720166</v>
+      </c>
+      <c r="U16" t="n">
+        <v>34.09467854540435</v>
       </c>
     </row>
     <row r="17">
@@ -2011,16 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0001069616862294262</v>
+        <v>-0.0006529153424409059</v>
       </c>
       <c r="G17" t="n">
-        <v>1.782694770490436e-05</v>
+        <v>-0.000108819223740151</v>
       </c>
       <c r="H17" t="n">
-        <v>16.89994642424934</v>
+        <v>-103.1606241056631</v>
       </c>
       <c r="I17" t="n">
-        <v>3565.389540980872</v>
+        <v>-21763.84474803019</v>
+      </c>
+      <c r="J17" t="n">
+        <v>103.1606241056634</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.116195150090789</v>
+      </c>
+      <c r="L17" t="n">
+        <v>173.3137672412556</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.05577790265808225</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-221.6594246672689</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-7.807193706494331</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-103.1606241056634</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-4.116195150090789</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-23.3137672412556</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.05577790265808225</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-368.2231787802656</v>
+      </c>
+      <c r="U17" t="n">
+        <v>32.50436460703907</v>
       </c>
     </row>
     <row r="18">
@@ -2042,16 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>8.330404797397828e-09</v>
+        <v>-0.0001055740783166281</v>
       </c>
       <c r="G18" t="n">
-        <v>1.041300599674728e-09</v>
+        <v>-1.319675978957852e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0009871529684916426</v>
+        <v>-12.51052828052043</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2082601199349457</v>
+        <v>-2639.351957915703</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12.51052828051979</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-20.32886904320844</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-29.95136551373676</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.1399243619677715</v>
+      </c>
+      <c r="N18" t="n">
+        <v>119.8137459613649</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-64.67502263175106</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-12.51052828051979</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>20.32886904320844</v>
+      </c>
+      <c r="R18" t="n">
+        <v>29.95136551373676</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1399243619677715</v>
+      </c>
+      <c r="T18" t="n">
+        <v>119.7971781485292</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-97.95592971391648</v>
       </c>
     </row>
     <row r="19">
@@ -2073,16 +2745,52 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.895203629343107e-05</v>
+        <v>-0.0001740734582367232</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.369004536678884e-06</v>
+        <v>-2.175918227959039e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-6.985816300771582</v>
+        <v>-20.62770480105169</v>
       </c>
       <c r="I19" t="n">
-        <v>-1473.800907335777</v>
+        <v>-4351.836455918078</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20.62770480103791</v>
+      </c>
+      <c r="K19" t="n">
+        <v>32.77195795069392</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-526.4796256065976</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.1674336878034616</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2151.8736934672</v>
+      </c>
+      <c r="O19" t="n">
+        <v>97.65662236329339</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-20.62770480103791</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-32.77195795069392</v>
+      </c>
+      <c r="R19" t="n">
+        <v>526.4796256065976</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1674336878034616</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2059.96331138558</v>
+      </c>
+      <c r="U19" t="n">
+        <v>164.5190412422579</v>
       </c>
     </row>
     <row r="20">
@@ -2104,16 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.350365771435763e-06</v>
+        <v>0.0002293761867009914</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.187957214294704e-07</v>
+        <v>2.867202333762392e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.397018343915138</v>
+        <v>27.18107812406748</v>
       </c>
       <c r="I20" t="n">
-        <v>-83.75914428589408</v>
+        <v>5734.404667524784</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-27.18107812406743</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-120.3262129092034</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-38.31274245297931</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.03750559622947636</v>
+      </c>
+      <c r="N20" t="n">
+        <v>148.6013299059929</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-164.5905998148902</v>
+      </c>
+      <c r="P20" t="n">
+        <v>27.18107812406743</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-79.67378709079662</v>
+      </c>
+      <c r="R20" t="n">
+        <v>38.31274245297931</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.03750559622947636</v>
+      </c>
+      <c r="T20" t="n">
+        <v>157.9006097178416</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.980896541263149</v>
       </c>
     </row>
     <row r="21">
@@ -2135,16 +2879,52 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0001108653565218033</v>
+        <v>0.001057196239915736</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.385816956522542e-05</v>
+        <v>0.0001321495299894671</v>
       </c>
       <c r="H21" t="n">
-        <v>-13.13754474783369</v>
+        <v>125.2777544300148</v>
       </c>
       <c r="I21" t="n">
-        <v>-2771.633913045083</v>
+        <v>26429.90599789341</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-125.2777544300188</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-7.751465002016882</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-505.9794931517395</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.185348779389393</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2024.094570697432</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.250969248789389</v>
+      </c>
+      <c r="P21" t="n">
+        <v>125.2777544300188</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7.751465002016882</v>
+      </c>
+      <c r="R21" t="n">
+        <v>505.9794931517395</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.185348779389393</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2023.741374516484</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-64.26268926492449</v>
       </c>
     </row>
     <row r="22">
@@ -2166,16 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>1.079176821296504e-06</v>
+        <v>-7.115239550292696e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>1.34897102662063e-07</v>
+        <v>-8.89404943786587e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1278824533236357</v>
+        <v>-8.431558867096845</v>
       </c>
       <c r="I22" t="n">
-        <v>26.9794205324126</v>
+        <v>-1778.809887573174</v>
+      </c>
+      <c r="J22" t="n">
+        <v>8.431558867094282</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.907094219625492</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-37.44745119590817</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.7264335376073403</v>
+      </c>
+      <c r="N22" t="n">
+        <v>149.7634828585553</v>
+      </c>
+      <c r="O22" t="n">
+        <v>34.86921080087586</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-8.431558867094282</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-5.907094219625492</v>
+      </c>
+      <c r="R22" t="n">
+        <v>37.44745119590817</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.7264335376073403</v>
+      </c>
+      <c r="T22" t="n">
+        <v>149.81612670871</v>
+      </c>
+      <c r="U22" t="n">
+        <v>12.38754295612807</v>
       </c>
     </row>
     <row r="23">
@@ -2197,16 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0004310107409973285</v>
+        <v>0.00162463354023501</v>
       </c>
       <c r="G23" t="n">
-        <v>5.387634262466606e-05</v>
+        <v>0.0002030791925293762</v>
       </c>
       <c r="H23" t="n">
-        <v>51.07477280818343</v>
+        <v>192.5190745178487</v>
       </c>
       <c r="I23" t="n">
-        <v>10775.26852493321</v>
+        <v>40615.83850587524</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-192.5190745177679</v>
+      </c>
+      <c r="K23" t="n">
+        <v>66.80885951768202</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-357.2856302055961</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.09736451574406163</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1908.094331492271</v>
+      </c>
+      <c r="O23" t="n">
+        <v>169.9159291470286</v>
+      </c>
+      <c r="P23" t="n">
+        <v>192.5190745177679</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-66.80885951768202</v>
+      </c>
+      <c r="R23" t="n">
+        <v>357.2856302055961</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.09736451574406163</v>
+      </c>
+      <c r="T23" t="n">
+        <v>950.1907101524979</v>
+      </c>
+      <c r="U23" t="n">
+        <v>364.5549469944276</v>
       </c>
     </row>
     <row r="24">
@@ -2228,16 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>8.554620075755526e-07</v>
+        <v>1.503836553162774e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>1.069327509469441e-07</v>
+        <v>1.879795691453467e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>0.101372247897703</v>
+        <v>1.782046315497887</v>
       </c>
       <c r="I24" t="n">
-        <v>21.38655018938881</v>
+        <v>375.9591382906935</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.782046315493062</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-50.12585500958915</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-37.37605177413763</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.113355533693104</v>
+      </c>
+      <c r="N24" t="n">
+        <v>99.01739029673753</v>
+      </c>
+      <c r="O24" t="n">
+        <v>191.0147515798436</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.782046315493062</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-149.8741449904109</v>
+      </c>
+      <c r="R24" t="n">
+        <v>37.37605177413763</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-1.113355533693104</v>
+      </c>
+      <c r="T24" t="n">
+        <v>199.9910238963635</v>
+      </c>
+      <c r="U24" t="n">
+        <v>207.9784083434427</v>
       </c>
     </row>
     <row r="25">
@@ -2259,16 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.000483218051875095</v>
+        <v>0.001076486602899607</v>
       </c>
       <c r="G25" t="n">
-        <v>6.040225648438688e-05</v>
+        <v>0.0001345608253624508</v>
       </c>
       <c r="H25" t="n">
-        <v>57.26133914719876</v>
+        <v>127.5636624436034</v>
       </c>
       <c r="I25" t="n">
-        <v>12080.45129687737</v>
+        <v>26912.16507249017</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-127.5636624436593</v>
+      </c>
+      <c r="K25" t="n">
+        <v>18.3901745281176</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-431.74139011613</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.2914433421853525</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1726.358908332749</v>
+      </c>
+      <c r="O25" t="n">
+        <v>112.3335280626782</v>
+      </c>
+      <c r="P25" t="n">
+        <v>127.5636624436593</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-18.3901745281176</v>
+      </c>
+      <c r="R25" t="n">
+        <v>431.74139011613</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2914433421853525</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1727.57221259629</v>
+      </c>
+      <c r="U25" t="n">
+        <v>34.78786816226227</v>
       </c>
     </row>
     <row r="26">
@@ -2290,16 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.105421811008037e-09</v>
+        <v>-0.0001051822652722301</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.381777263760047e-10</v>
+        <v>-1.314778315902876e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0006049924846044524</v>
+        <v>-12.46409843475926</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1276355452752009</v>
+        <v>-2629.556631805752</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12.46409843476431</v>
+      </c>
+      <c r="K26" t="n">
+        <v>18.50839878808893</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-21.63355112027549</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.0926466731507235</v>
+      </c>
+      <c r="N26" t="n">
+        <v>86.54154973736216</v>
+      </c>
+      <c r="O26" t="n">
+        <v>90.66689582718391</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-12.46409843476431</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-18.50839878808893</v>
+      </c>
+      <c r="R26" t="n">
+        <v>21.63355112027549</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.0926466731507235</v>
+      </c>
+      <c r="T26" t="n">
+        <v>86.52685922484176</v>
+      </c>
+      <c r="U26" t="n">
+        <v>57.40029447752659</v>
       </c>
     </row>
     <row r="27">
@@ -2321,16 +3281,52 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.148366756508761e-05</v>
+        <v>0.001536654425072115</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.685458445635951e-06</v>
+        <v>0.0001920818031340144</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.285814606462882</v>
+        <v>182.0935493710456</v>
       </c>
       <c r="I27" t="n">
-        <v>-1537.09168912719</v>
+        <v>38416.36062680287</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-182.0935493709985</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-5.959963132195512</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-274.7542534582191</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.1276615161915826</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1115.269199423327</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-57.08303073159067</v>
+      </c>
+      <c r="P27" t="n">
+        <v>182.0935493709985</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5.959963132195512</v>
+      </c>
+      <c r="R27" t="n">
+        <v>274.7542534582191</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.1276615161915826</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1082.764828242425</v>
+      </c>
+      <c r="U27" t="n">
+        <v>9.403325674026803</v>
       </c>
     </row>
     <row r="28">
@@ -2352,16 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>8.43648272623454e-07</v>
+        <v>5.565559936138165e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>1.054560340779317e-07</v>
+        <v>6.956949920172706e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0999723203058793</v>
+        <v>6.595188524323725</v>
       </c>
       <c r="I28" t="n">
-        <v>21.09120681558635</v>
+        <v>1391.389984034541</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-6.595188524341211</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-81.51814703991795</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-28.75694233772689</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.0207219479267835</v>
+      </c>
+      <c r="N28" t="n">
+        <v>112.8281492501357</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-9.458774506152935</v>
+      </c>
+      <c r="P28" t="n">
+        <v>6.595188524341211</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-118.4818529600821</v>
+      </c>
+      <c r="R28" t="n">
+        <v>28.75694233772689</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.0207219479267835</v>
+      </c>
+      <c r="T28" t="n">
+        <v>117.2273894516794</v>
+      </c>
+      <c r="U28" t="n">
+        <v>157.3135981868093</v>
       </c>
     </row>
     <row r="29">
@@ -2383,16 +3415,52 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.218114160484346e-05</v>
+        <v>0.001113614290146003</v>
       </c>
       <c r="G29" t="n">
-        <v>-9.022642700605432e-06</v>
+        <v>0.0001392017862682504</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.553465280173949</v>
+        <v>131.9632933823014</v>
       </c>
       <c r="I29" t="n">
-        <v>-1804.528540121086</v>
+        <v>27840.35725365008</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-131.9632933821995</v>
+      </c>
+      <c r="K29" t="n">
+        <v>30.92861067592477</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-251.5946504736163</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-0.1361498444878597</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1008.826844862238</v>
+      </c>
+      <c r="O29" t="n">
+        <v>157.0517121625711</v>
+      </c>
+      <c r="P29" t="n">
+        <v>131.9632933821995</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-30.92861067592477</v>
+      </c>
+      <c r="R29" t="n">
+        <v>251.5946504736163</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.1361498444878597</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1003.930358926692</v>
+      </c>
+      <c r="U29" t="n">
+        <v>90.37717324482674</v>
       </c>
     </row>
     <row r="30">
@@ -2414,16 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>2.115887465237165e-10</v>
+        <v>-0.0001054896281654782</v>
       </c>
       <c r="G30" t="n">
-        <v>2.644859331546456e-11</v>
+        <v>-1.318620352068478e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>2.507326646306041e-05</v>
+        <v>-12.50052093760917</v>
       </c>
       <c r="I30" t="n">
-        <v>0.005289718663092913</v>
+        <v>-2637.240704136956</v>
+      </c>
+      <c r="J30" t="n">
+        <v>12.50052093761042</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5.061241533179555</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-7.019509614552399</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.02083464748759228</v>
+      </c>
+      <c r="N30" t="n">
+        <v>28.07581587500367</v>
+      </c>
+      <c r="O30" t="n">
+        <v>36.90020666256169</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-12.50052093761042</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-5.061241533179555</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7.019509614552399</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-0.02083464748759228</v>
+      </c>
+      <c r="T30" t="n">
+        <v>28.08026104141551</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.589725602874751</v>
       </c>
     </row>
     <row r="31">
@@ -2445,16 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0003239896173865553</v>
+        <v>0.0006230945216358919</v>
       </c>
       <c r="G31" t="n">
-        <v>-4.049870217331941e-05</v>
+        <v>7.788681520448648e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>-38.3927696603068</v>
+        <v>73.83670081385318</v>
       </c>
       <c r="I31" t="n">
-        <v>-8099.740434663882</v>
+        <v>15577.36304089729</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-73.8367008138448</v>
+      </c>
+      <c r="K31" t="n">
+        <v>7.450730348091383</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-92.85403857811413</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-0.04360590404072028</v>
+      </c>
+      <c r="N31" t="n">
+        <v>375.8292647536747</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-3.533797077073132</v>
+      </c>
+      <c r="P31" t="n">
+        <v>73.8367008138448</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-7.450730348091383</v>
+      </c>
+      <c r="R31" t="n">
+        <v>92.85403857811413</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.04360590404072028</v>
+      </c>
+      <c r="T31" t="n">
+        <v>367.0030438712382</v>
+      </c>
+      <c r="U31" t="n">
+        <v>63.13963986180471</v>
       </c>
     </row>
     <row r="32">
@@ -2476,16 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.327185613145265e-07</v>
+        <v>0.0001133110714135466</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.658982016431582e-08</v>
+        <v>1.416388392669332e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.01572714951577139</v>
+        <v>13.42736196250527</v>
       </c>
       <c r="I32" t="n">
-        <v>-3.317964032863163</v>
+        <v>2832.776785338664</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-13.42736196250189</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-94.94054335937926</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-8.314361537792287</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-0.005102500778656233</v>
+      </c>
+      <c r="N32" t="n">
+        <v>34.05107264136433</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-63.08419102967977</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13.42736196250189</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-105.0594566406207</v>
+      </c>
+      <c r="R32" t="n">
+        <v>8.314361537792287</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.005102500778656233</v>
+      </c>
+      <c r="T32" t="n">
+        <v>32.46381966097396</v>
+      </c>
+      <c r="U32" t="n">
+        <v>103.5598441546466</v>
       </c>
     </row>
     <row r="33">
@@ -2507,16 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0003223055183949608</v>
+        <v>0.0006898370413459531</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.02881897993701e-05</v>
+        <v>8.622963016824414e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>-38.19320392980286</v>
+        <v>81.74568939949545</v>
       </c>
       <c r="I33" t="n">
-        <v>-8057.63795987402</v>
+        <v>17245.92603364883</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-81.74568939954042</v>
+      </c>
+      <c r="K33" t="n">
+        <v>17.54355711260374</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-94.84626256787126</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.04054494606610064</v>
+      </c>
+      <c r="N33" t="n">
+        <v>368.2282812810421</v>
+      </c>
+      <c r="O33" t="n">
+        <v>103.504066251989</v>
+      </c>
+      <c r="P33" t="n">
+        <v>81.74568939954042</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-17.54355711260374</v>
+      </c>
+      <c r="R33" t="n">
+        <v>94.84626256787126</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.04054494606610064</v>
+      </c>
+      <c r="T33" t="n">
+        <v>390.5418192619279</v>
+      </c>
+      <c r="U33" t="n">
+        <v>36.84439064884054</v>
       </c>
     </row>
   </sheetData>
@@ -2530,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP33"/>
+  <dimension ref="A1:AS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2541,205 +3753,220 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>i</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>L (M)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>N_tension (+) (KN)</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Δu_local_x (M)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>axial strain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>N (KN)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>sigma (KN/M^2)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>u_g_1 (M)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>u_g_2 (M)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>u_g_3 (M)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>u_g_4 (rad)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>u_g_5 (rad)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>u_g_6 (rad)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>u_g_7 (M)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>u_g_8 (M)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>u_g_9 (M)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>u_g_10 (rad)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>u_g_11 (rad)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>u_g_12 (rad)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>u_l_1 (M)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>u_l_2 (M)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>u_l_3 (M)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>u_l_4 (rad)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>u_l_5 (rad)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>u_l_6 (rad)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>u_l_7 (M)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>u_l_8 (M)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>u_l_9 (M)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>u_l_10 (rad)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>u_l_11 (rad)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>u_l_12 (rad)</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>q_l_1 (KN)</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>q_l_2 (KN)</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>q_l_3 (KN)</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>q_l_4 (KN*M)</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>q_l_5 (KN*M)</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>q_l_6 (KN*M)</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>q_l_7 (KN)</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>q_l_8 (KN)</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>q_l_9 (KN)</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>q_l_10 (KN*M)</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>q_l_11 (KN*M)</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>q_l_12 (KN*M)</t>
         </is>
@@ -2749,29 +3976,31 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
-        <v>-129.0333320192031</v>
-      </c>
       <c r="F2" t="n">
-        <v>-27222.22194497956</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.001455921596786739</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1380.213673753829</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>291184.3193573478</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2783,31 +4012,31 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0128097137669131</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.00429138568796626</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0009334393834214193</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005875642721208698</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -2819,87 +4048,98 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.00429138568796626</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0128097137669131</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0005875642721208698</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="AC2" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.0009334393834214193</v>
+        <v>-3.757925951552276</v>
       </c>
       <c r="AE2" t="n">
-        <v>129.0333320192032</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3677966592998273</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3.119530228461257</v>
+        <v>0.03630395006709138</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.001672298312959399</v>
+        <v>-1380.213673753829</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.398789852761077</v>
+        <v>-13.20417079465767</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.794135121631332</v>
+        <v>475.6982651531055</v>
       </c>
       <c r="AK2" t="n">
-        <v>-129.0333320192032</v>
+        <v>0.01454786787215924</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.3677966592998273</v>
+        <v>-1878.351598355772</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.119530228461257</v>
+        <v>-66.4774354336206</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.001672298312959399</v>
+        <v>1380.213673753829</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.318391518006464</v>
+        <v>13.20417079465767</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4126448341676316</v>
+        <v>-475.6982651531055</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.01454786787215924</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-975.8379925628601</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-12.74758933432537</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>-119.379425596438</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-25185.53282625273</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.001030760455960402</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>977.1609122504611</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>206152.0911920804</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2911,31 +4151,31 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.012844443226954</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.004291377357561463</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.000755565984787582</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0009331687918622317</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005888482869970602</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -2947,87 +4187,98 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.000755565984787582</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.004291377357561463</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.012844443226954</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0005888482869970602</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.0009331687918622317</v>
+        <v>-3.723395957223965</v>
       </c>
       <c r="AE3" t="n">
-        <v>119.379425596438</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3679948422204428</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.092972341477125</v>
+        <v>0.03628902410958178</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.001675952816837787</v>
+        <v>-977.1609122504613</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.354240678936237</v>
+        <v>-13.18917439722999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.79452943263938</v>
+        <v>418.6737544032946</v>
       </c>
       <c r="AK3" t="n">
-        <v>-119.379425596438</v>
+        <v>0.0998835270571985</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.3679948422204428</v>
+        <v>-1755.785178255167</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.092972341477125</v>
+        <v>-66.42140103278049</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001675952816837787</v>
+        <v>977.1609122504613</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.203593369926512</v>
+        <v>13.18917439722999</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4134396206832771</v>
+        <v>-418.6737544032946</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.0998835270571985</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-756.2573481646002</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-12.71364535059946</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
-        <v>119.4256515558396</v>
-      </c>
       <c r="F4" t="n">
-        <v>25195.28513836278</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0.001032719886363857</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-979.018452272936</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-206543.9772727713</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3039,31 +4290,31 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01290339526324743</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005039316492279876</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007558585541508834</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.001070169352779969</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.006773559198856145</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00057958013234802</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3075,87 +4326,98 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007558585541508834</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.005039316492279876</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01290339526324743</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00057958013234802</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.006773559198856145</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.001070169352779969</v>
+        <v>-3.723221883765729</v>
       </c>
       <c r="AE4" t="n">
-        <v>-119.4256515558396</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.451106080371859</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.829596308885847</v>
+        <v>-0.04214837918573356</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.001649574222836672</v>
+        <v>979.0184522729362</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.4763551195039941</v>
+        <v>16.26814280349655</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2.145243562172753</v>
+        <v>554.9044043380102</v>
       </c>
       <c r="AK4" t="n">
-        <v>119.4256515558396</v>
+        <v>-0.07155857263245415</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.451106080371859</v>
+        <v>-1953.2035400049</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1.829596308885847</v>
+        <v>79.99422900793247</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001649574222836672</v>
+        <v>-979.0184522729362</v>
       </c>
       <c r="AO4" t="n">
-        <v>-10.50122273381109</v>
+        <v>-16.26814280349655</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.5613929200583989</v>
+        <v>-404.9044043380101</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.07155857263245415</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-926.2228860231605</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>17.61462781304681</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
-        <v>128.9871060598018</v>
-      </c>
       <c r="F5" t="n">
-        <v>27212.46963286958</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.001453962166383287</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-1378.356133731356</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-290792.4332766574</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3167,31 +4429,31 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0129205791234349</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005042666858051312</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0008163740889860875</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.001296178924107323</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.00752700330388983</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0005839113268276019</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3203,3642 +4465,3959 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0008163740889860875</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005042666858051312</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0129205791234349</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0005839113268276019</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.00752700330388983</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.001296178924107323</v>
+        <v>-3.758983147792192</v>
       </c>
       <c r="AE5" t="n">
-        <v>-128.9871060598018</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.2846854211465715</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.382906261097865</v>
+        <v>-0.05052610874595759</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001661901468663174</v>
+        <v>1378.356133731357</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.578736338415123</v>
+        <v>10.12520238831702</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1.813228667279133</v>
+        <v>550.7235761049859</v>
       </c>
       <c r="AK5" t="n">
-        <v>128.9871060598018</v>
+        <v>0.1850957102150153</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.2846854211465715</v>
+        <v>-1953.662995332046</v>
       </c>
       <c r="AM5" t="n">
-        <v>-2.382906261097865</v>
+        <v>67.76492763695965</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.001661901468663174</v>
+        <v>-1378.356133731357</v>
       </c>
       <c r="AO5" t="n">
-        <v>-12.71870122817207</v>
+        <v>-10.12520238831702</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.105116140399705</v>
+        <v>-400.7235761049859</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.1850957102150153</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-900.678461297869</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-7.013713307057571</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>9</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
-        <v>-125.2769258009596</v>
-      </c>
       <c r="F6" t="n">
-        <v>-26429.73118163703</v>
+        <v>0.005343562120812355</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0128097137669131</v>
+        <v>0.0008905936868020591</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.00429138568796626</v>
+        <v>844.282815088352</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>178118.7373604118</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009334393834214193</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0005875642721208698</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08422531326366116</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01382352321936229</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001609558593798498</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001091937175770063</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004967274058364416</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.00429138568796626</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0128097137669131</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005875642721208698</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="W6" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0009334393834214193</v>
+        <v>-3.757925951552276</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.001609558593798498</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.01382352321936229</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.08422531326366116</v>
+        <v>0.03630395006709138</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.004967274058364416</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.001091937175770063</v>
+        <v>-8.658378534736178</v>
       </c>
       <c r="AE6" t="n">
-        <v>125.2769258009596</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.8524819372759898</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="AG6" t="n">
-        <v>9.531946826075149</v>
+        <v>0.04556477868176344</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.01246532785315471</v>
+        <v>-844.2828150883522</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.528444111040393</v>
+        <v>-33.46616407719057</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.674734178165965</v>
+        <v>370.7493797662693</v>
       </c>
       <c r="AK6" t="n">
-        <v>-125.2769258009596</v>
+        <v>0.4268812346987415</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.8524819372759898</v>
+        <v>-1047.763457591656</v>
       </c>
       <c r="AM6" t="n">
-        <v>-9.531946826075149</v>
+        <v>-107.251505406429</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.01246532785315471</v>
+        <v>844.2828150883522</v>
       </c>
       <c r="AO6" t="n">
-        <v>-55.66323684541052</v>
+        <v>33.46616407719057</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.440157445489972</v>
+        <v>-370.7493797662693</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.4268812346987415</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1176.73282100596</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-93.54547905671429</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>-116.3204620044577</v>
-      </c>
       <c r="F7" t="n">
-        <v>-24540.18185748053</v>
+        <v>0.003041978811124054</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.012844443226954</v>
+        <v>0.0005069964685206757</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.004291377357561463</v>
+        <v>480.6326521576005</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.000755565984787582</v>
+        <v>101399.2937041351</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009331687918622317</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0005888482869970602</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1297075743306731</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01382244404254099</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.001491771440511998</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001093009262885102</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005274182961996149</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.000755565984787582</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.004291377357561463</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="U7" t="n">
-        <v>0.012844443226954</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0005888482869970602</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0009331687918622317</v>
+        <v>-3.723395957223965</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.001491771440511998</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.01382244404254099</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1297075743306731</v>
+        <v>0.03628902410958178</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.005274182961996149</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.001093009262885102</v>
+        <v>-10.03693211708712</v>
       </c>
       <c r="AE7" t="n">
-        <v>116.3204620044577</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.8516246884485901</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.378911652591935</v>
+        <v>0.04561220557379464</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.01333518330576664</v>
+        <v>-480.6326521576007</v>
       </c>
       <c r="AI7" t="n">
-        <v>11.91776839139045</v>
+        <v>-33.45060406740529</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.673156013902694</v>
+        <v>418.9725901611122</v>
       </c>
       <c r="AK7" t="n">
-        <v>-116.3204620044577</v>
+        <v>0.3991908776797221</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.8516246884485901</v>
+        <v>-1395.756269664567</v>
       </c>
       <c r="AM7" t="n">
-        <v>-6.378911652591935</v>
+        <v>-107.2509664857333</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.01333518330576664</v>
+        <v>480.6326521576007</v>
       </c>
       <c r="AO7" t="n">
-        <v>-50.19123830694207</v>
+        <v>33.45060406740529</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.436592116788844</v>
+        <v>-418.9725901611122</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.3991908776797221</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-1118.079271302104</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-93.45265791869829</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>11</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
-        <v>116.5747656721505</v>
-      </c>
       <c r="F8" t="n">
-        <v>24593.83242028492</v>
+        <v>-0.003106655500755174</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01290339526324743</v>
+        <v>-0.000517775916792529</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005039316492279876</v>
+        <v>-490.8515691193175</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0007558585541508834</v>
+        <v>-103555.1833585058</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.001070169352779969</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.006773559198856145</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00057958013234802</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1292765635896758</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02019608507901711</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001493673526759431</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0007558585541508834</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.005039316492279876</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01290339526324743</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00057958013234802</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.006773559198856145</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001070169352779969</v>
+        <v>-3.723221883765729</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001493673526759431</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02019608507901711</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1292765635896758</v>
+        <v>-0.04214837918573356</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-10.03855675062735</v>
       </c>
       <c r="AE8" t="n">
-        <v>-116.5747656721505</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-2.946744263671342</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>-23.69294771336545</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.001649574222836672</v>
+        <v>490.8515691193177</v>
       </c>
       <c r="AI8" t="n">
-        <v>66.06640933294278</v>
+        <v>118.6258911179426</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-8.048307469956848</v>
+        <v>1194.292273501664</v>
       </c>
       <c r="AK8" t="n">
-        <v>116.5747656721505</v>
+        <v>0.07155857263245415</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.946744263671342</v>
+        <v>-2994.386493514121</v>
       </c>
       <c r="AM8" t="n">
-        <v>23.69294771336545</v>
+        <v>324.687872756385</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.001649574222836672</v>
+        <v>-490.8515691193177</v>
       </c>
       <c r="AO8" t="n">
-        <v>76.09127694724987</v>
+        <v>-118.6258911179426</v>
       </c>
       <c r="AP8" t="n">
-        <v>-9.632158112071203</v>
+        <v>-1044.292273501664</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.07155857263245415</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-3721.36714749586</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>387.0674739512706</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>12</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
-        <v>125.0226221332669</v>
-      </c>
       <c r="F9" t="n">
-        <v>26376.08061883268</v>
+        <v>-0.005278885431181244</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0129205791234349</v>
+        <v>-0.0008798142385302073</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005042666858051312</v>
+        <v>-834.0638981266366</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0008163740889860875</v>
+        <v>-175962.8477060414</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.001296178924107323</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.00752700330388983</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0005839113268276019</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08374209521178606</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02019522961700954</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001607656507551068</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.002179807909866056</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.000889993047089781</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004663764944930242</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0008163740889860875</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005042666858051312</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0129205791234349</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005839113268276019</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.00752700330388983</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="X9" t="n">
-        <v>0.001296178924107323</v>
+        <v>-3.758983147792192</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001607656507551068</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02019522961700954</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.08374209521178606</v>
+        <v>-0.05052610874595759</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.004663764944930242</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.000889993047089781</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.002179807909866056</v>
+        <v>-8.659455021339078</v>
       </c>
       <c r="AE9" t="n">
-        <v>-125.0226221332669</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="AF9" t="n">
-        <v>-1.165401890069396</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="AG9" t="n">
-        <v>-11.24073000206838</v>
+        <v>-0.09096723747714046</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.01161189106690751</v>
+        <v>834.0638981266368</v>
       </c>
       <c r="AI9" t="n">
-        <v>28.81080241617309</v>
+        <v>45.05774551440441</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-4.150091119669648</v>
+        <v>446.3275434442011</v>
       </c>
       <c r="AK9" t="n">
-        <v>125.0226221332669</v>
+        <v>0.4551684177415671</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.165401890069396</v>
+        <v>-1123.453614995791</v>
       </c>
       <c r="AM9" t="n">
-        <v>11.24073000206838</v>
+        <v>165.0996718042885</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.01161189106690751</v>
+        <v>-834.0638981266368</v>
       </c>
       <c r="AO9" t="n">
-        <v>38.63357759623716</v>
+        <v>-45.05774551440441</v>
       </c>
       <c r="AP9" t="n">
-        <v>-2.842320220746724</v>
+        <v>-296.3275434442011</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.4551684177415671</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-1104.511645669415</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>105.246801282138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>13</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" t="n">
-        <v>-109.09600842395</v>
-      </c>
       <c r="F10" t="n">
-        <v>-23016.0355324789</v>
+        <v>0.002374012492255152</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.08422531326366116</v>
+        <v>0.0003956687487091919</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01382352321936229</v>
+        <v>375.0939737763139</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.001609558593798498</v>
+        <v>79133.74974183837</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001091937175770063</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004967274058364416</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4746865315037455</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02091067317803995</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.002300039659772865</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0005792017214737926</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="R10" t="n">
-        <v>0.007070915224504301</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.001609558593798498</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.01382352321936229</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08422531326366116</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="V10" t="n">
-        <v>0.004967274058364416</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.001091937175770063</v>
+        <v>-8.658378534736178</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.002300039659772865</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.02091067317803995</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.4746865315037455</v>
+        <v>0.04556477868176344</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.007070915224504301</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.0005792017214737926</v>
+        <v>-12.10067564645607</v>
       </c>
       <c r="AE10" t="n">
-        <v>109.09600842395</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5115208725133691</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="AG10" t="n">
-        <v>-47.2594010135611</v>
+        <v>0.02662802448650984</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.005987286395936592</v>
+        <v>-375.0939737763142</v>
       </c>
       <c r="AI10" t="n">
-        <v>136.6173781238849</v>
+        <v>-23.50754841617129</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.155138381360866</v>
+        <v>237.2786231035455</v>
       </c>
       <c r="AK10" t="n">
-        <v>-109.09600842395</v>
+        <v>0.3455385960838586</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.5115208725133691</v>
+        <v>-550.1129580527219</v>
       </c>
       <c r="AM10" t="n">
-        <v>47.2594010135611</v>
+        <v>-56.50944714402618</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.005987286395936592</v>
+        <v>375.0939737763142</v>
       </c>
       <c r="AO10" t="n">
-        <v>146.9390279574816</v>
+        <v>23.50754841617129</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.913986853719347</v>
+        <v>-237.2786231035455</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.3455385960838586</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-873.5587805685493</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-84.53584335300144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>14</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>6</v>
       </c>
-      <c r="E11" t="n">
-        <v>-107.9775931058531</v>
-      </c>
       <c r="F11" t="n">
-        <v>-22780.08293372429</v>
+        <v>0.002145286274060163</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1297075743306731</v>
+        <v>0.0003575477123433605</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01382244404254099</v>
+        <v>338.9552313015058</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.001491771440511998</v>
+        <v>71509.54246867209</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001093009262885102</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005274182961996149</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5353453752792312</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02091067828346176</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.002175173928523727</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0005791054802541305</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="R11" t="n">
-        <v>0.007070520459421152</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.001491771440511998</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01382244404254099</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1297075743306731</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="V11" t="n">
-        <v>0.005274182961996149</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.001093009262885102</v>
+        <v>-10.03693211708712</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.002175173928523727</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.02091067828346176</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.5353453752792312</v>
+        <v>0.04561220557379464</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.007070520459421152</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.0005791054802541305</v>
+        <v>-14.61043109294954</v>
       </c>
       <c r="AE11" t="n">
-        <v>107.9775931058531</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.5110662028374233</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="AG11" t="n">
-        <v>-45.1658524631494</v>
+        <v>0.02661478979054551</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.005112652877286546</v>
+        <v>-338.9552313015058</v>
       </c>
       <c r="AI11" t="n">
-        <v>124.1293751529342</v>
+        <v>-23.4738521565387</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.152909809365353</v>
+        <v>232.360609862576</v>
       </c>
       <c r="AK11" t="n">
-        <v>-107.9775931058531</v>
+        <v>0.3731922717374728</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.5110662028374233</v>
+        <v>-315.6461386515213</v>
       </c>
       <c r="AM11" t="n">
-        <v>45.1658524631494</v>
+        <v>-56.36346879001178</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.005112652877286546</v>
+        <v>338.9552313015058</v>
       </c>
       <c r="AO11" t="n">
-        <v>146.8657396259622</v>
+        <v>23.4738521565387</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.91348740765919</v>
+        <v>-232.360609862576</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.3731922717374728</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1078.517520523936</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-84.47964414922058</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>15</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
-        <v>107.7853772268509</v>
-      </c>
       <c r="F12" t="n">
-        <v>22739.53106051707</v>
+        <v>-0.002092006254182372</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1292765635896758</v>
+        <v>-0.0003486677090303953</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02019608507901711</v>
+        <v>-330.5369881608148</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001493673526759431</v>
+        <v>-69733.54180607905</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5354068589467963</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03157201090228527</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.002175859458574943</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0007408499310935353</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.192528065686288</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001493673526759431</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02019608507901711</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1292765635896758</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-10.03855675062735</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.002175859458574943</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.03157201090228527</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.5354068589467963</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.192528065686288</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0007408499310935353</v>
+        <v>-14.61196774737462</v>
       </c>
       <c r="AE12" t="n">
-        <v>-107.785377226851</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="AF12" t="n">
-        <v>-2.257832754063596</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="AG12" t="n">
-        <v>42.29196241976337</v>
+        <v>-0.03319060518208777</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.02012612215266922</v>
+        <v>330.5369881608146</v>
       </c>
       <c r="AI12" t="n">
-        <v>15.59488134856298</v>
+        <v>98.68818091821899</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-7.321727211200004</v>
+        <v>967.6109033612859</v>
       </c>
       <c r="AK12" t="n">
-        <v>107.785377226851</v>
+        <v>0.7017888395369127</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.257832754063596</v>
+        <v>-2988.329852586897</v>
       </c>
       <c r="AM12" t="n">
-        <v>-42.29196241976337</v>
+        <v>320.6255905894019</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.02012612215266922</v>
+        <v>-330.5369881608146</v>
       </c>
       <c r="AO12" t="n">
-        <v>-269.3466558671432</v>
+        <v>-98.68818091821899</v>
       </c>
       <c r="AP12" t="n">
-        <v>-6.225269313181572</v>
+        <v>-817.6109033612859</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.7017888395369127</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-2367.335567580818</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>271.503494919912</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>16</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>6</v>
       </c>
-      <c r="E13" t="n">
-        <v>109.2882243029522</v>
-      </c>
       <c r="F13" t="n">
-        <v>23056.58740568612</v>
+        <v>-0.002427292512132957</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.08374209521178606</v>
+        <v>-0.0004045487520221595</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02019522961700954</v>
+        <v>-383.5122169170072</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001607656507551068</v>
+        <v>-80909.75040443189</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.002179807909866056</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000889993047089781</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004663764944930242</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4747587126453503</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03157116725401265</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="O13" t="n">
-        <v>0.002299354129721651</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0008078657293793546</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1919280290521911</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="R13" t="n">
-        <v>0.007069048702360571</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001607656507551068</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02019522961700954</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08374209521178606</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="V13" t="n">
-        <v>0.004663764944930242</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.000889993047089781</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="X13" t="n">
-        <v>0.002179807909866056</v>
+        <v>-8.659455021339078</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.002299354129721651</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.03157116725401265</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.4747587126453503</v>
+        <v>-0.09096723747714046</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.007069048702360571</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.1919280290521911</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0008078657293793546</v>
+        <v>-12.10178926074621</v>
       </c>
       <c r="AE13" t="n">
-        <v>-109.2882243029522</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.5951861240858296</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="AG13" t="n">
-        <v>46.23457071985531</v>
+        <v>-0.03715388464293796</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.006845807617301707</v>
+        <v>383.5122169170072</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.664434484208982</v>
+        <v>28.44961730178392</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.7703211586973282</v>
+        <v>309.8323268183962</v>
       </c>
       <c r="AK13" t="n">
-        <v>109.2882243029522</v>
+        <v>0.3176639268975212</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.5951861240858296</v>
+        <v>-621.8472626633337</v>
       </c>
       <c r="AM13" t="n">
-        <v>-46.23457071985531</v>
+        <v>45.52697080804194</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.006845807617301707</v>
+        <v>-383.5122169170072</v>
       </c>
       <c r="AO13" t="n">
-        <v>-280.0718588033409</v>
+        <v>-28.44961730178392</v>
       </c>
       <c r="AP13" t="n">
-        <v>-2.800795585817648</v>
+        <v>-159.8323268183962</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.3176639268975212</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-787.1466982470427</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>125.1707330026616</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>17</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
-        <v>-16.87038074214141</v>
-      </c>
       <c r="F14" t="n">
-        <v>-3559.152055304095</v>
+        <v>0.0006447200771039496</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4746865315037455</v>
+        <v>0.0001074533461839916</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.02091067317803995</v>
+        <v>101.865772182424</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.002300039659772865</v>
+        <v>21490.66923679832</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0005792017214737926</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007070915224504301</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8693932027947637</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02354482424360938</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.002406814221431988</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001818926669167243</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.05018136607334805</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="R14" t="n">
-        <v>0.007409214359710549</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.002300039659772865</v>
+        <v>-0.009077683545820888</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.02091067317803995</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4746865315037455</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="V14" t="n">
-        <v>0.007070915224504301</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.0005792017214737926</v>
+        <v>-12.10067564645607</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.002406814221431988</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.02354482424360938</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.8693932027947637</v>
+        <v>0.02662802448650984</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.007409214359710549</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.05018136607334805</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.0001818926669167243</v>
+        <v>-13.74971682084649</v>
       </c>
       <c r="AE14" t="n">
-        <v>16.87038074214138</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.08654741543147892</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="AG14" t="n">
-        <v>-38.27999740640961</v>
+        <v>0.009077683545820888</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.0009628513848177825</v>
+        <v>-101.8657721824238</v>
       </c>
       <c r="AI14" t="n">
-        <v>130.0274324957424</v>
+        <v>-5.043036174986128</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0.03436645407779437</v>
+        <v>86.80693093240026</v>
       </c>
       <c r="AK14" t="n">
-        <v>-16.87038074214138</v>
+        <v>0.05581601372114864</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.08654741543147892</v>
+        <v>-130.2789316849898</v>
       </c>
       <c r="AM14" t="n">
-        <v>38.27999740640961</v>
+        <v>-2.14185622884861</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0009628513848177825</v>
+        <v>101.8657721824238</v>
       </c>
       <c r="AO14" t="n">
-        <v>99.65255194271532</v>
+        <v>5.043036174986128</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.5536509466666679</v>
+        <v>-86.80693093240026</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.05581601372114864</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-390.5626539094091</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-28.11636082106827</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>18</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="E15" t="n">
-        <v>-16.51879152681601</v>
-      </c>
       <c r="F15" t="n">
-        <v>-3484.977115362026</v>
+        <v>0.0005432565124276027</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5353453752792312</v>
+        <v>9.054275207126712e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02091067828346176</v>
+        <v>85.83452896356123</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.002175173928523727</v>
+        <v>18108.55041425342</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0005791054802541305</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007070520459421152</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.929500914833618</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02354482403202064</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.002279723241984587</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0001819140044221856</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.05021271910715217</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="R15" t="n">
-        <v>0.007409200793266503</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.002175173928523727</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.02091067828346176</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5353453752792312</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="V15" t="n">
-        <v>0.007070520459421152</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.0005791054802541305</v>
+        <v>-14.61043109294954</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.002279723241984587</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.02354482403202064</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.929500914833618</v>
+        <v>0.02661478979054551</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.007409200793266503</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.05021271910715217</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.0001819140044221856</v>
+        <v>-16.28729671562621</v>
       </c>
       <c r="AE15" t="n">
-        <v>16.51879152681602</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.08660153265071635</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="AG15" t="n">
-        <v>-38.30597618363233</v>
+        <v>0.00908168820024597</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.0009639363347906139</v>
+        <v>-85.8345289635613</v>
       </c>
       <c r="AI15" t="n">
-        <v>130.3136959230324</v>
+        <v>-5.049790589544841</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0.03411709416349318</v>
+        <v>68.77545927978912</v>
       </c>
       <c r="AK15" t="n">
-        <v>-16.51879152681602</v>
+        <v>0.05592852579814611</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.08660153265071635</v>
+        <v>-36.84432557254138</v>
       </c>
       <c r="AM15" t="n">
-        <v>38.30597618363233</v>
+        <v>-2.174876591812904</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.0009639363347906139</v>
+        <v>85.8345289635613</v>
       </c>
       <c r="AO15" t="n">
-        <v>99.52216117876142</v>
+        <v>5.049790589544841</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5537262900677842</v>
+        <v>-68.77545927978912</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.05592852579814611</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-375.8084301061951</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-28.12386694545614</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>19</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="n">
-        <v>16.48922584470822</v>
-      </c>
       <c r="F16" t="n">
-        <v>3478.739629685278</v>
+        <v>-0.0005350612470906464</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5354068589467963</v>
+        <v>-8.917687451510774e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03157201090228527</v>
+        <v>-84.53967704032213</v>
       </c>
       <c r="I16" t="n">
-        <v>0.002175859458574943</v>
+        <v>-17835.37490302155</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0007408499310935353</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.192528065686288</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9298249044510045</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="N16" t="n">
-        <v>0.03489745300852468</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="O16" t="n">
-        <v>0.002280221647465502</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.0002293826508512665</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.009055914509505684</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.00740935996088564</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="S16" t="n">
-        <v>0.002175859458574943</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="T16" t="n">
-        <v>0.03157201090228527</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5354068589467963</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.192528065686288</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0007408499310935353</v>
+        <v>-14.61196774737462</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.002280221647465502</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.03489745300852468</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.9298249044510045</v>
+        <v>-0.03319060518208777</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.00740935996088564</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.009055914509505684</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0002293826508512665</v>
+        <v>-16.28791981014785</v>
       </c>
       <c r="AE16" t="n">
-        <v>-16.48922584470824</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.1023036088998994</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="AG16" t="n">
-        <v>38.47960731311419</v>
+        <v>-0.01134630288189326</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.0009620561975437515</v>
+        <v>84.5396770403222</v>
       </c>
       <c r="AI16" t="n">
-        <v>-264.6109672842299</v>
+        <v>5.976631614420171</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0715749606795768</v>
+        <v>171.1038425458343</v>
       </c>
       <c r="AK16" t="n">
-        <v>16.48922584470824</v>
+        <v>0.05544883212311946</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.1023036088998994</v>
+        <v>-209.6149089029861</v>
       </c>
       <c r="AM16" t="n">
-        <v>-38.47960731311419</v>
+        <v>1.765111141116449</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0009620561975437515</v>
+        <v>-84.5396770403222</v>
       </c>
       <c r="AO16" t="n">
-        <v>33.73332340554468</v>
+        <v>-5.976631614420171</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.6853966140789787</v>
+        <v>-21.10384254583424</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.05544883212311946</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-367.0081463720166</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>34.09467854540435</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>20</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
-        <v>16.89994642424934</v>
-      </c>
       <c r="F17" t="n">
-        <v>3565.389540980872</v>
+        <v>-0.0006529153424409059</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4747587126453503</v>
+        <v>-0.000108819223740151</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03157116725401265</v>
+        <v>-103.1606241056631</v>
       </c>
       <c r="I17" t="n">
-        <v>0.002299354129721651</v>
+        <v>-21763.84474803019</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0008078657293793546</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1919280290521911</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="L17" t="n">
-        <v>0.007069048702360571</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8697155083131587</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="N17" t="n">
-        <v>0.03489758572708599</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="O17" t="n">
-        <v>0.002406315815951078</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.0002052034834714622</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.008780674266115432</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="R17" t="n">
-        <v>0.007409370087792433</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="S17" t="n">
-        <v>0.002299354129721651</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="T17" t="n">
-        <v>0.03157116725401265</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4747587126453503</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="V17" t="n">
-        <v>0.007069048702360571</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.1919280290521911</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0008078657293793546</v>
+        <v>-12.10178926074621</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.002406315815951078</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.03489758572708599</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.8697155083131587</v>
+        <v>-0.03715388464293796</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.007409370087792433</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.008780674266115432</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0002052034834714622</v>
+        <v>-13.75040665788783</v>
       </c>
       <c r="AE17" t="n">
-        <v>-16.89994642424938</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.07084533918181979</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="AG17" t="n">
-        <v>38.10636627696992</v>
+        <v>-0.009916345241901936</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.0009686070200752989</v>
+        <v>103.1606241056634</v>
       </c>
       <c r="AI17" t="n">
-        <v>-262.8435392864565</v>
+        <v>4.116195150090789</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.2334340444263781</v>
+        <v>173.3137672412556</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.89994642424938</v>
+        <v>0.05577790265808225</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.07084533918181979</v>
+        <v>-221.6594246672689</v>
       </c>
       <c r="AM17" t="n">
-        <v>-38.10636627696992</v>
+        <v>-7.807193706494331</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.0009686070200752989</v>
+        <v>-103.1606241056634</v>
       </c>
       <c r="AO17" t="n">
-        <v>34.20534162463713</v>
+        <v>-4.116195150090789</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.6585060795172986</v>
+        <v>-23.3137672412556</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.05577790265808225</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-368.2231787802656</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>32.50436460703907</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>6</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>8</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.0009871529684916426</v>
-      </c>
       <c r="F18" t="n">
-        <v>0.2082601199349457</v>
+        <v>-0.0001055740783166281</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0128097137669131</v>
+        <v>-1.319675978957852e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.00429138568796626</v>
+        <v>-12.51052828052043</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>-2639.351957915703</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0009334393834214193</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0005875642721208698</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.012844443226954</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.004291377357561463</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.000755565984787582</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="P18" t="n">
-        <v>0.0009331687918622317</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0005888482869970602</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.00429138568796626</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0128097137669131</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="V18" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0009334393834214193</v>
+        <v>-3.757925951552276</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0005875642721208698</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.004291377357561463</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.012844443226954</v>
+        <v>0.03630395006709138</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.000755565984787582</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.0009331687918622317</v>
+        <v>-3.723395957223965</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0005888482869970602</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0009871529684915004</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.4860676932973318</v>
+        <v>0.03628902410958178</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.7706173641192945</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.005870551405175642</v>
+        <v>12.51052828051979</v>
       </c>
       <c r="AI18" t="n">
-        <v>-3.082619634792527</v>
+        <v>-20.32886904320844</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.943558144933041</v>
+        <v>-29.95136551373676</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0009871529684915004</v>
+        <v>-0.1399243619677715</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.4860676932973318</v>
+        <v>119.8137459613649</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.7706173641192945</v>
+        <v>-64.67502263175106</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.005870551405175642</v>
+        <v>-12.51052828051979</v>
       </c>
       <c r="AO18" t="n">
-        <v>-3.082319278161829</v>
+        <v>20.32886904320844</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.944983401445612</v>
+        <v>29.95136551373676</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.1399243619677715</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>119.7971781485292</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-97.95592971391648</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>7</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>8</v>
       </c>
-      <c r="E19" t="n">
-        <v>-6.985816300771582</v>
-      </c>
       <c r="F19" t="n">
-        <v>-1473.800907335777</v>
+        <v>-0.0001740734582367232</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.012844443226954</v>
+        <v>-2.175918227959039e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.004291377357561463</v>
+        <v>-20.62770480105169</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.000755565984787582</v>
+        <v>-4351.836455918078</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0009331687918622317</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0005888482869970602</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.01290339526324743</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="N19" t="n">
-        <v>0.005039316492279876</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0007558585541508834</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.001070169352779969</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.006773559198856145</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="R19" t="n">
-        <v>0.00057958013234802</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.012844443226954</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.004291377357561463</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.000755565984787582</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0009331687918622317</v>
+        <v>3.723395957223965</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.002804491425006571</v>
+        <v>0.1623366982634615</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0005888482869970602</v>
+        <v>0.006184562735762412</v>
       </c>
       <c r="Y19" t="n">
-        <v>-0.01290339526324743</v>
+        <v>-0.03628902410958178</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.005039316492279876</v>
+        <v>0.6753566419530859</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.0007558585541508834</v>
+        <v>-0.03509421220928596</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.001070169352779969</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.006773559198856145</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.00057958013234802</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="AE19" t="n">
-        <v>6.985816300771603</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.4846169991967247</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.829580956099572</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.004276356424140083</v>
+        <v>20.62770480103791</v>
       </c>
       <c r="AI19" t="n">
-        <v>-13.11549120991177</v>
+        <v>32.77195795069392</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-1.933324170956682</v>
+        <v>-526.4796256065976</v>
       </c>
       <c r="AK19" t="n">
-        <v>-6.985816300771603</v>
+        <v>-0.1674336878034616</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.4846169991967247</v>
+        <v>2151.8736934672</v>
       </c>
       <c r="AM19" t="n">
-        <v>-3.829580956099572</v>
+        <v>97.65662236329339</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.004276356424140083</v>
+        <v>-20.62770480103791</v>
       </c>
       <c r="AO19" t="n">
-        <v>-17.5211564388848</v>
+        <v>-32.77195795069392</v>
       </c>
       <c r="AP19" t="n">
-        <v>-1.943611822617117</v>
+        <v>526.4796256065976</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.1674336878034616</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>2059.96331138558</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>164.5190412422579</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>7</v>
-      </c>
-      <c r="C20" t="n">
-        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.397018343915138</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>-83.75914428589408</v>
+        <v>0.0002293761867009914</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.01290339526324743</v>
+        <v>2.867202333762392e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.005039316492279876</v>
+        <v>27.18107812406748</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0007558585541508834</v>
+        <v>5734.404667524784</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.001070169352779969</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.006773559198856145</v>
+        <v>-0.1923970678416461</v>
       </c>
       <c r="L20" t="n">
-        <v>0.00057958013234802</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0129205791234349</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="N20" t="n">
-        <v>0.005042666858051312</v>
+        <v>0.5925544959336078</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0008163740889860875</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.001296178924107323</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.00752700330388983</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0005839113268276019</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.005039316492279876</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.01290339526324743</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0007558585541508834</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="V20" t="n">
-        <v>0.006773559198856145</v>
+        <v>0.1923970678416461</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.001070169352779969</v>
+        <v>3.723221883765729</v>
       </c>
       <c r="X20" t="n">
-        <v>0.00057958013234802</v>
+        <v>-0.006196319318183139</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.005042666858051312</v>
+        <v>-0.5925544959336078</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.0129205791234349</v>
+        <v>0.04214837918573356</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.0008163740889860875</v>
+        <v>0.0251422011951866</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.00752700330388983</v>
+        <v>0.1926264440283471</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.001296178924107323</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.0005839113268276019</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.3970183439151924</v>
+        <v>-0.6101246851582274</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.4860915153326111</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.978695072410547</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.001608313378052671</v>
+        <v>-27.18107812406743</v>
       </c>
       <c r="AI20" t="n">
-        <v>-3.789344977555507</v>
+        <v>-120.3262129092034</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.941962248394275</v>
+        <v>-38.31274245297931</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.3970183439151924</v>
+        <v>0.03750559622947636</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.4860915153326111</v>
+        <v>148.6013299059929</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0.978695072410547</v>
+        <v>-164.5905998148902</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.001608313378052671</v>
+        <v>27.18107812406743</v>
       </c>
       <c r="AO20" t="n">
-        <v>-4.040215601728869</v>
+        <v>-79.67378709079662</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.946769874266612</v>
+        <v>38.31274245297931</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-0.03750559622947636</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>157.9006097178416</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.980896541263149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>8</v>
       </c>
-      <c r="E21" t="n">
-        <v>-13.13754474783369</v>
-      </c>
       <c r="F21" t="n">
-        <v>-2771.633913045083</v>
+        <v>0.001057196239915736</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0129205791234349</v>
+        <v>0.0001321495299894671</v>
       </c>
       <c r="H21" t="n">
-        <v>0.005042666858051312</v>
+        <v>125.2777544300148</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0008163740889860875</v>
+        <v>26429.90599789341</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.001296178924107323</v>
+        <v>3.758983147792192</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.00752700330388983</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0005839113268276019</v>
+        <v>-0.008723772998299724</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0128097137669131</v>
+        <v>0.05052610874595759</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.00429138568796626</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0008166666583493869</v>
+        <v>-0.06503362791338377</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0009334393834214193</v>
+        <v>3.757925951552276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0005875642721208698</v>
+        <v>0.008735529580720434</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0129205791234349</v>
+        <v>-0.03630395006709138</v>
       </c>
       <c r="T21" t="n">
-        <v>0.005042666858051312</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0008163740889860875</v>
+        <v>-0.005111413036164057</v>
       </c>
       <c r="V21" t="n">
-        <v>0.001296178924107323</v>
+        <v>-3.758983147792192</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.00752700330388983</v>
+        <v>-0.1926264440283471</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0005839113268276019</v>
+        <v>0.008723772998299724</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.0128097137669131</v>
+        <v>-0.05052610874595759</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.00429138568796626</v>
+        <v>0.6101246851582274</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.0008166666583493869</v>
+        <v>0.06503362791338377</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.0009334393834214193</v>
+        <v>-3.757925951552276</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.432319915852241e-05</v>
+        <v>0.1624422723417782</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.0005875642721208698</v>
+        <v>-0.008735529580720434</v>
       </c>
       <c r="AE21" t="n">
-        <v>13.13754474783354</v>
+        <v>0.03630395006709138</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.4836981250076524</v>
+        <v>0.6098064904006163</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.98578885412428</v>
+        <v>0.005111413036164057</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.004759377541070969</v>
+        <v>-125.2777544300188</v>
       </c>
       <c r="AI21" t="n">
-        <v>-16.09049287462299</v>
+        <v>-7.751465002016882</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.936819884668374</v>
+        <v>-505.9794931517395</v>
       </c>
       <c r="AK21" t="n">
-        <v>-13.13754474783354</v>
+        <v>-0.185348779389393</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.4836981250076524</v>
+        <v>2024.094570697432</v>
       </c>
       <c r="AM21" t="n">
-        <v>-2.98578885412428</v>
+        <v>2.250969248789389</v>
       </c>
       <c r="AN21" t="n">
-        <v>-0.004759377541070969</v>
+        <v>125.2777544300188</v>
       </c>
       <c r="AO21" t="n">
-        <v>-7.795817958371241</v>
+        <v>7.751465002016882</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.932765115392846</v>
+        <v>505.9794931517395</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.185348779389393</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2023.741374516484</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-64.26268926492449</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>8</v>
       </c>
-      <c r="E22" t="n">
-        <v>0.1278824533236357</v>
-      </c>
       <c r="F22" t="n">
-        <v>26.9794205324126</v>
+        <v>-7.115239550292696e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.08422531326366116</v>
+        <v>-8.89404943786587e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.01382352321936229</v>
+        <v>-8.431558867096845</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.001609558593798498</v>
+        <v>-1778.809887573174</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001091937175770063</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004967274058364416</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1297075743306731</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.01382244404254099</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.001491771440511998</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="P22" t="n">
-        <v>0.001093009262885102</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="R22" t="n">
-        <v>0.005274182961996149</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.01382352321936229</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08422531326366116</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.001609558593798498</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.001091937175770063</v>
+        <v>-8.658378534736178</v>
       </c>
       <c r="X22" t="n">
-        <v>0.004967274058364416</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.01382244404254099</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.1297075743306731</v>
+        <v>0.04556477868176344</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.001491771440511998</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.001093009262885102</v>
+        <v>-10.03693211708712</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.005274182961996149</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.1278824533235365</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.4699913075608446</v>
+        <v>0.04561220557379464</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.8972267294513363</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.017371821545506</v>
+        <v>8.431558867094282</v>
       </c>
       <c r="AI22" t="n">
-        <v>-3.588311909456498</v>
+        <v>5.907094219625492</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-2.050299671758985</v>
+        <v>-37.44745119590817</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.1278824533235365</v>
+        <v>-0.7264335376073403</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.4699913075608446</v>
+        <v>149.7634828585553</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.8972267294513363</v>
+        <v>34.86921080087586</v>
       </c>
       <c r="AN22" t="n">
-        <v>-0.017371821545506</v>
+        <v>-8.431558867094282</v>
       </c>
       <c r="AO22" t="n">
-        <v>-3.589501926154191</v>
+        <v>-5.907094219625492</v>
       </c>
       <c r="AP22" t="n">
-        <v>-1.709630788727772</v>
+        <v>37.44745119590817</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.7264335376073403</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>149.81612670871</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>12.38754295612807</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>10</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>11</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>8</v>
       </c>
-      <c r="E23" t="n">
-        <v>51.07477280818343</v>
-      </c>
       <c r="F23" t="n">
-        <v>10775.26852493321</v>
+        <v>0.00162463354023501</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1297075743306731</v>
+        <v>0.0002030791925293762</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.01382244404254099</v>
+        <v>192.5190745178487</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.001491771440511998</v>
+        <v>40615.83850587524</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001093009262885102</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005274182961996149</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1292765635896758</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="N23" t="n">
-        <v>0.02019608507901711</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="O23" t="n">
-        <v>0.001493673526759431</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1297075743306731</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.01382244404254099</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.001491771440511998</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.001093009262885102</v>
+        <v>10.03693211708712</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.04477003649144745</v>
+        <v>0.5436509443436122</v>
       </c>
       <c r="X23" t="n">
-        <v>0.005274182961996149</v>
+        <v>0.009226541546886466</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.1292765635896758</v>
+        <v>-0.04561220557379464</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.02019608507901711</v>
+        <v>0.8629762354412365</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.001493673526759431</v>
+        <v>-0.1753504665291883</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="AE23" t="n">
-        <v>-51.07477280818421</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>-1.344674528781243</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>18.32485482265832</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.002333154388081661</v>
+        <v>-192.5190745177679</v>
       </c>
       <c r="AI23" t="n">
-        <v>-98.1467895433866</v>
+        <v>66.80885951768202</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-2.451526571217111</v>
+        <v>-357.2856302055961</v>
       </c>
       <c r="AK23" t="n">
-        <v>51.07477280818421</v>
+        <v>-0.09736451574406163</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.344674528781243</v>
+        <v>1908.094331492271</v>
       </c>
       <c r="AM23" t="n">
-        <v>-18.32485482265832</v>
+        <v>169.9159291470286</v>
       </c>
       <c r="AN23" t="n">
-        <v>-0.002333154388081661</v>
+        <v>192.5190745177679</v>
       </c>
       <c r="AO23" t="n">
-        <v>-48.45204903787994</v>
+        <v>-66.80885951768202</v>
       </c>
       <c r="AP23" t="n">
-        <v>-8.305869659032837</v>
+        <v>357.2856302055961</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.09736451574406163</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>950.1907101524979</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>364.5549469944276</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>11</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>12</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>0.101372247897703</v>
-      </c>
       <c r="F24" t="n">
-        <v>21.38655018938881</v>
+        <v>1.503836553162774e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1292765635896758</v>
+        <v>1.879795691453467e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02019608507901711</v>
+        <v>1.782046315497887</v>
       </c>
       <c r="I24" t="n">
-        <v>0.001493673526759431</v>
+        <v>375.9591382906935</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-0.7997579802013167</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.08374209521178606</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.02019522961700954</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.001607656507551068</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.002179807909866056</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.000889993047089781</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="R24" t="n">
-        <v>0.004663764944930242</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.02019608507901711</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1292765635896758</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="U24" t="n">
-        <v>0.001493673526759431</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.7997579802013167</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>10.03855675062735</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.009302974818938313</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.02019522961700954</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.08374209521178606</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.001607656507551068</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.000889993047089781</v>
+        <v>0.7997730185668483</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.002179807909866056</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.004663764944930242</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.1013722478974159</v>
+        <v>-0.5215719617301026</v>
       </c>
       <c r="AF24" t="n">
-        <v>-2.797138457246934</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.8954836885431163</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.001899792850518571</v>
+        <v>-1.782046315493062</v>
       </c>
       <c r="AI24" t="n">
-        <v>-2.372141364196803</v>
+        <v>-50.12585500958915</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-13.77694337342402</v>
+        <v>-37.37605177413763</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.1013722478974159</v>
+        <v>1.113355533693104</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.797138457246934</v>
+        <v>99.01739029673753</v>
       </c>
       <c r="AM24" t="n">
-        <v>-0.8954836885431163</v>
+        <v>191.0147515798436</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.001899792850518571</v>
+        <v>1.782046315493062</v>
       </c>
       <c r="AO24" t="n">
-        <v>-4.791728144148126</v>
+        <v>-149.8741449904109</v>
       </c>
       <c r="AP24" t="n">
-        <v>-8.600164284551454</v>
+        <v>37.37605177413763</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>-1.113355533693104</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>199.9910238963635</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>207.9784083434427</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>12</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>9</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>8</v>
       </c>
-      <c r="E25" t="n">
-        <v>57.26133914719876</v>
-      </c>
       <c r="F25" t="n">
-        <v>12080.45129687737</v>
+        <v>0.001076486602899607</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.08374209521178606</v>
+        <v>0.0001345608253624508</v>
       </c>
       <c r="H25" t="n">
-        <v>0.02019522961700954</v>
+        <v>127.5636624436034</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001607656507551068</v>
+        <v>26912.16507249017</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.002179807909866056</v>
+        <v>8.659455021339078</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.000889993047089781</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004663764944930242</v>
+        <v>-0.01400265842948097</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.08422531326366116</v>
+        <v>0.09096723747714046</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.01382352321936229</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.001609558593798498</v>
+        <v>-0.2249576665793398</v>
       </c>
       <c r="P25" t="n">
-        <v>0.001091937175770063</v>
+        <v>8.658378534736178</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="R25" t="n">
-        <v>0.004967274058364416</v>
+        <v>0.01407909170153279</v>
       </c>
       <c r="S25" t="n">
-        <v>0.08374209521178606</v>
+        <v>-0.04556477868176344</v>
       </c>
       <c r="T25" t="n">
-        <v>0.02019522961700954</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.001607656507551068</v>
+        <v>-0.1550967117141002</v>
       </c>
       <c r="V25" t="n">
-        <v>0.002179807909866056</v>
+        <v>-8.659455021339078</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.000889993047089781</v>
+        <v>-0.7997730185668483</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.004663764944930242</v>
+        <v>0.01400265842948097</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.08422531326366116</v>
+        <v>-0.09096723747714046</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.01382352321936229</v>
+        <v>0.5215719617301026</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.001609558593798498</v>
+        <v>0.2249576665793398</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.001091937175770063</v>
+        <v>-8.658378534736178</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.03663188585751671</v>
+        <v>0.5437220967391151</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.004967274058364416</v>
+        <v>-0.01407909170153279</v>
       </c>
       <c r="AE25" t="n">
-        <v>-57.26133914720049</v>
+        <v>0.04556477868176344</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.4688435180864579</v>
+        <v>0.5226650286341942</v>
       </c>
       <c r="AG25" t="n">
-        <v>15.28369064755826</v>
+        <v>0.1550967117141002</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.006983917394338641</v>
+        <v>-127.5636624436593</v>
       </c>
       <c r="AI25" t="n">
-        <v>-41.29801208044611</v>
+        <v>18.3901745281176</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-1.706926514389863</v>
+        <v>-431.74139011613</v>
       </c>
       <c r="AK25" t="n">
-        <v>57.26133914720049</v>
+        <v>-0.2914433421853525</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.4688435180864579</v>
+        <v>1726.358908332749</v>
       </c>
       <c r="AM25" t="n">
-        <v>-15.28369064755826</v>
+        <v>112.3335280626782</v>
       </c>
       <c r="AN25" t="n">
-        <v>-0.006983917394338641</v>
+        <v>127.5636624436593</v>
       </c>
       <c r="AO25" t="n">
-        <v>-80.97151310002</v>
+        <v>-18.3901745281176</v>
       </c>
       <c r="AP25" t="n">
-        <v>-2.043821630301796</v>
+        <v>431.74139011613</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.2914433421853525</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1727.57221259629</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>34.78786816226227</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>13</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>14</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>8</v>
       </c>
-      <c r="E26" t="n">
-        <v>-0.0006049924846044524</v>
-      </c>
       <c r="F26" t="n">
-        <v>-0.1276355452752009</v>
+        <v>-0.0001051822652722301</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4746865315037455</v>
+        <v>-1.314778315902876e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.02091067317803995</v>
+        <v>-12.46409843475926</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.002300039659772865</v>
+        <v>-2629.556631805752</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0005792017214737926</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="L26" t="n">
-        <v>0.007070915224504301</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5353453752792312</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.02091067828346176</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.002175173928523727</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0005791054802541305</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="R26" t="n">
-        <v>0.007070520459421152</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.02091067317803995</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4746865315037455</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.002300039659772865</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.0005792017214737926</v>
+        <v>-12.10067564645607</v>
       </c>
       <c r="X26" t="n">
-        <v>0.007070915224504301</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.02091067828346176</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.5353453752792312</v>
+        <v>0.02662802448650984</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.002175173928523727</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.0005791054802541305</v>
+        <v>-14.61043109294954</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.007070520459421152</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.0006049924845683563</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.4259383269525188</v>
+        <v>0.02661478979054551</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.4691515325611346</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.0005340168767505038</v>
+        <v>12.46409843476431</v>
       </c>
       <c r="AI26" t="n">
-        <v>-1.87665954412145</v>
+        <v>18.50839878808893</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-1.703534213188931</v>
+        <v>-21.63355112027549</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0.0006049924845683563</v>
+        <v>-0.0926466731507235</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.4259383269525188</v>
+        <v>86.54154973736216</v>
       </c>
       <c r="AM26" t="n">
-        <v>-0.4691515325611346</v>
+        <v>90.66689582718391</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.0005340168767505038</v>
+        <v>-12.46409843476431</v>
       </c>
       <c r="AO26" t="n">
-        <v>-1.876552716367626</v>
+        <v>-18.50839878808893</v>
       </c>
       <c r="AP26" t="n">
-        <v>-1.703972402431248</v>
+        <v>21.63355112027549</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.0926466731507235</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>86.52685922484176</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>57.40029447752659</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>14</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>15</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
-      <c r="E27" t="n">
-        <v>-7.285814606462882</v>
-      </c>
       <c r="F27" t="n">
-        <v>-1537.09168912719</v>
+        <v>0.001536654425072115</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5353453752792312</v>
+        <v>0.0001920818031340144</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.02091067828346176</v>
+        <v>182.0935493710456</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.002175173928523727</v>
+        <v>38416.36062680287</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0005791054802541305</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="L27" t="n">
-        <v>0.007070520459421152</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.5354068589467963</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="N27" t="n">
-        <v>0.03157201090228527</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="O27" t="n">
-        <v>0.002175859458574943</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.0007408499310935353</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.192528065686288</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5353453752792312</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.02091067828346176</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.002175173928523727</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="V27" t="n">
-        <v>0.0005791054802541305</v>
+        <v>14.61043109294954</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.02940762806372589</v>
+        <v>0.8554961959361138</v>
       </c>
       <c r="X27" t="n">
-        <v>0.007070520459421152</v>
+        <v>0.01137182782094663</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.5354068589467963</v>
+        <v>-0.02661478979054551</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.03157201090228527</v>
+        <v>0.3475225990409564</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.002175859458574943</v>
+        <v>-0.3064720755180301</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.0007408499310935353</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.192528065686288</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="AE27" t="n">
-        <v>7.285814606468193</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.4250696626701282</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="AG27" t="n">
-        <v>91.92795311159833</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.002817597128069056</v>
+        <v>-182.0935493709985</v>
       </c>
       <c r="AI27" t="n">
-        <v>-277.1799695658713</v>
+        <v>-5.959963132195512</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.699823685888751</v>
+        <v>-274.7542534582191</v>
       </c>
       <c r="AK27" t="n">
-        <v>-7.285814606468193</v>
+        <v>-0.1276615161915826</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.4250696626701282</v>
+        <v>1115.269199423327</v>
       </c>
       <c r="AM27" t="n">
-        <v>-91.92795311159833</v>
+        <v>-57.08303073159067</v>
       </c>
       <c r="AN27" t="n">
-        <v>-0.002817597128069056</v>
+        <v>182.0935493709985</v>
       </c>
       <c r="AO27" t="n">
-        <v>-458.2436553269152</v>
+        <v>5.959963132195512</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.700733615472268</v>
+        <v>274.7542534582191</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.1276615161915826</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1082.764828242425</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9.403325674026803</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>15</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>16</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
-      <c r="E28" t="n">
-        <v>0.0999723203058793</v>
-      </c>
       <c r="F28" t="n">
-        <v>21.09120681558635</v>
+        <v>5.565559936138165e-05</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.5354068589467963</v>
+        <v>6.956949920172706e-06</v>
       </c>
       <c r="H28" t="n">
-        <v>0.03157201090228527</v>
+        <v>6.595188524323725</v>
       </c>
       <c r="I28" t="n">
-        <v>0.002175859458574943</v>
+        <v>1391.389984034541</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.0007408499310935353</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.192528065686288</v>
+        <v>-1.299417015686306</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4747587126453503</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="N28" t="n">
-        <v>0.03157116725401265</v>
+        <v>0.3182393817608644</v>
       </c>
       <c r="O28" t="n">
-        <v>0.002299354129721651</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.0008078657293793546</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.1919280290521911</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="R28" t="n">
-        <v>0.007069048702360571</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.03157201090228527</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.5354068589467963</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="U28" t="n">
-        <v>0.002175859458574943</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="V28" t="n">
-        <v>0.192528065686288</v>
+        <v>1.299417015686306</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.0007408499310935353</v>
+        <v>14.61196774737462</v>
       </c>
       <c r="X28" t="n">
-        <v>0.0070713402158027</v>
+        <v>-0.01139498107312069</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0.03157116725401265</v>
+        <v>-0.3182393817608644</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.4747587126453503</v>
+        <v>0.03319060518208777</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.002299354129721651</v>
+        <v>-0.246574457134591</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.1919280290521911</v>
+        <v>1.299472671285667</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.0008078657293793546</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.007069048702360571</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.09997232030627856</v>
+        <v>-0.3085318025519207</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.4252608373087696</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.6318017294556362</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.001280847430476129</v>
+        <v>-6.595188524341211</v>
       </c>
       <c r="AI28" t="n">
-        <v>-2.490013149773915</v>
+        <v>-81.51814703991795</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-1.699771559274666</v>
+        <v>-28.75694233772689</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.09997232030627856</v>
+        <v>-0.0207219479267835</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.4252608373087696</v>
+        <v>112.8281492501357</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0.6318017294556362</v>
+        <v>-9.458774506152935</v>
       </c>
       <c r="AN28" t="n">
-        <v>-0.001280847430476129</v>
+        <v>6.595188524341211</v>
       </c>
       <c r="AO28" t="n">
-        <v>-2.564400685871174</v>
+        <v>-118.4818529600821</v>
       </c>
       <c r="AP28" t="n">
-        <v>-1.702315139195463</v>
+        <v>28.75694233772689</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0.0207219479267835</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>117.2273894516794</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>157.3135981868093</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>16</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>13</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>8</v>
       </c>
-      <c r="E29" t="n">
-        <v>-8.553465280173949</v>
-      </c>
       <c r="F29" t="n">
-        <v>-1804.528540121086</v>
+        <v>0.001113614290146003</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4747587126453503</v>
+        <v>0.0001392017862682504</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03157116725401265</v>
+        <v>131.9632933823014</v>
       </c>
       <c r="I29" t="n">
-        <v>0.002299354129721651</v>
+        <v>27840.35725365008</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0008078657293793546</v>
+        <v>12.10178926074621</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1919280290521911</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="L29" t="n">
-        <v>0.007069048702360571</v>
+        <v>-0.01642995094161392</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4746865315037455</v>
+        <v>0.03715388464293796</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.02091067317803995</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.002300039659772865</v>
+        <v>-0.3365693165703608</v>
       </c>
       <c r="P29" t="n">
-        <v>0.0005792017214737926</v>
+        <v>12.10067564645607</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="R29" t="n">
-        <v>0.007070915224504301</v>
+        <v>0.01645310419378794</v>
       </c>
       <c r="S29" t="n">
-        <v>0.4747587126453503</v>
+        <v>-0.02662802448650984</v>
       </c>
       <c r="T29" t="n">
-        <v>0.03157116725401265</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.002299354129721651</v>
+        <v>-0.2765021643922128</v>
       </c>
       <c r="V29" t="n">
-        <v>0.0008078657293793546</v>
+        <v>-12.10178926074621</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.1919280290521911</v>
+        <v>-1.299472671285667</v>
       </c>
       <c r="X29" t="n">
-        <v>-0.007069048702360571</v>
+        <v>0.01642995094161392</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.4746865315037455</v>
+        <v>-0.03715388464293796</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.02091067317803995</v>
+        <v>0.3085318025519207</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.002300039659772865</v>
+        <v>0.3365693165703608</v>
       </c>
       <c r="AB29" t="n">
-        <v>-0.0005792017214737926</v>
+        <v>-12.10067564645607</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.02965779813211352</v>
+        <v>0.855601378201386</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.007070915224504301</v>
+        <v>-0.01645310419378794</v>
       </c>
       <c r="AE29" t="n">
-        <v>8.553465280172531</v>
+        <v>0.02662802448650984</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.4243684645970305</v>
+        <v>0.3041205539613382</v>
       </c>
       <c r="AG29" t="n">
-        <v>91.75647614924752</v>
+        <v>0.2765021643922128</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.002960855520090372</v>
+        <v>-131.9632933821995</v>
       </c>
       <c r="AI29" t="n">
-        <v>-457.085882757633</v>
+        <v>30.92861067592477</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-1.696437938598349</v>
+        <v>-251.5946504736163</v>
       </c>
       <c r="AK29" t="n">
-        <v>-8.553465280172531</v>
+        <v>-0.1361498444878597</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.4243684645970305</v>
+        <v>1008.826844862238</v>
       </c>
       <c r="AM29" t="n">
-        <v>-91.75647614924752</v>
+        <v>157.0517121625711</v>
       </c>
       <c r="AN29" t="n">
-        <v>-0.002960855520090372</v>
+        <v>131.9632933821995</v>
       </c>
       <c r="AO29" t="n">
-        <v>-276.965926436347</v>
+        <v>-30.92861067592477</v>
       </c>
       <c r="AP29" t="n">
-        <v>-1.698509778177888</v>
+        <v>251.5946504736163</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0.1361498444878597</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1003.930358926692</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>90.37717324482674</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>17</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>18</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
-      <c r="E30" t="n">
-        <v>2.507326646306041e-05</v>
-      </c>
       <c r="F30" t="n">
-        <v>0.005289718663092913</v>
+        <v>-0.0001054896281654782</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8693932027947637</v>
+        <v>-1.318620352068478e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.02354482424360938</v>
+        <v>-12.50052093760917</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.002406814221431988</v>
+        <v>-2637.240704136956</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0001818926669167243</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.05018136607334805</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="L30" t="n">
-        <v>0.007409214359710549</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.929500914833618</v>
+        <v>-0.009077683545820888</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.02354482403202064</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.002279723241984587</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0001819140044221856</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.05021271910715217</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="R30" t="n">
-        <v>0.007409200793266503</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.02354482424360938</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="T30" t="n">
-        <v>0.8693932027947637</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.002406814221431988</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.05018136607334805</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.0001818926669167243</v>
+        <v>-13.74971682084649</v>
       </c>
       <c r="X30" t="n">
-        <v>0.007409214359710549</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.02354482403202064</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.929500914833618</v>
+        <v>0.009077683545820888</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.002279723241984587</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.05021271910715217</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.0001819140044221856</v>
+        <v>-16.28729671562621</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.007409200793266503</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="AE30" t="n">
-        <v>-2.50732664426323e-05</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.08679347661657744</v>
+        <v>0.00908168820024597</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.1382091218960761</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="AH30" t="n">
-        <v>6.692666831263627e-05</v>
+        <v>12.50052093761042</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.5528246452687735</v>
+        <v>5.061241533179555</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.3471663770898772</v>
+        <v>-7.019509614552399</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.50732664426323e-05</v>
+        <v>0.02083464748759228</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.08679347661657744</v>
+        <v>28.07581587500367</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.1382091218960761</v>
+        <v>36.90020666256169</v>
       </c>
       <c r="AN30" t="n">
-        <v>-6.692666831263627e-05</v>
+        <v>-12.50052093761042</v>
       </c>
       <c r="AO30" t="n">
-        <v>-0.5528483298998356</v>
+        <v>-5.061241533179555</v>
       </c>
       <c r="AP30" t="n">
-        <v>-0.3471814358427991</v>
+        <v>7.019509614552399</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>-0.02083464748759228</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>28.08026104141551</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>3.589725602874751</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>18</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>19</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
-      <c r="E31" t="n">
-        <v>-38.3927696603068</v>
-      </c>
       <c r="F31" t="n">
-        <v>-8099.740434663882</v>
+        <v>0.0006230945216358919</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.929500914833618</v>
+        <v>7.788681520448648e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.02354482403202064</v>
+        <v>73.83670081385318</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.002279723241984587</v>
+        <v>15577.36304089729</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0001819140044221856</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.05021271910715217</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="L31" t="n">
-        <v>0.007409200793266503</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.9298249044510045</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="N31" t="n">
-        <v>0.03489745300852468</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="O31" t="n">
-        <v>0.002280221647465502</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.0002293826508512665</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.009055914509505684</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="R31" t="n">
-        <v>0.00740935996088564</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.929500914833618</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="T31" t="n">
-        <v>-0.02354482403202064</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.002279723241984587</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0001819140044221856</v>
+        <v>16.28729671562621</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.05021271910715217</v>
+        <v>0.9830577539201565</v>
       </c>
       <c r="X31" t="n">
-        <v>0.007409200793266503</v>
+        <v>0.01191508433337423</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.9298249044510045</v>
+        <v>-0.00908168820024597</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.03489745300852468</v>
+        <v>0.1184927986803802</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.002280221647465502</v>
+        <v>-0.3261226386362977</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0.0002293826508512665</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.009055914509505684</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.00740935996088564</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="AE31" t="n">
-        <v>38.39276966030593</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.08657645938408365</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="AG31" t="n">
-        <v>16.65700064871195</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.0008779601679875613</v>
+        <v>-73.8367008138448</v>
       </c>
       <c r="AI31" t="n">
-        <v>-99.52209425209293</v>
+        <v>7.450730348091383</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.346217499507711</v>
+        <v>-92.85403857811413</v>
       </c>
       <c r="AK31" t="n">
-        <v>-38.39276966030593</v>
+        <v>-0.04360590404072028</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.08657645938408365</v>
+        <v>375.8292647536747</v>
       </c>
       <c r="AM31" t="n">
-        <v>-16.65700064871195</v>
+        <v>-3.533797077073132</v>
       </c>
       <c r="AN31" t="n">
-        <v>-0.0008779601679875613</v>
+        <v>73.8367008138448</v>
       </c>
       <c r="AO31" t="n">
-        <v>-33.7339109376027</v>
+        <v>-7.450730348091383</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.3463941755649529</v>
+        <v>92.85403857811413</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.04360590404072028</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>367.0030438712382</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>63.13963986180471</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>19</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>20</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>8</v>
       </c>
-      <c r="E32" t="n">
-        <v>-0.01572714951577139</v>
-      </c>
       <c r="F32" t="n">
-        <v>-3.317964032863163</v>
+        <v>0.0001133110714135466</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.9298249044510045</v>
+        <v>1.416388392669332e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>0.03489745300852468</v>
+        <v>13.42736196250527</v>
       </c>
       <c r="I32" t="n">
-        <v>0.002280221647465502</v>
+        <v>2832.776785338664</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0002293826508512665</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="K32" t="n">
-        <v>0.009055914509505684</v>
+        <v>-1.457257327504276</v>
       </c>
       <c r="L32" t="n">
-        <v>0.00740935996088564</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8697155083131587</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="N32" t="n">
-        <v>0.03489758572708599</v>
+        <v>0.1105412483358429</v>
       </c>
       <c r="O32" t="n">
-        <v>0.002406315815951078</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.0002052034834714622</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.008780674266115432</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="R32" t="n">
-        <v>0.007409370087792433</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.03489745300852468</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="T32" t="n">
-        <v>-0.9298249044510045</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="U32" t="n">
-        <v>0.002280221647465502</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.009055914509505684</v>
+        <v>1.457257327504276</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.0002293826508512665</v>
+        <v>16.28791981014785</v>
       </c>
       <c r="X32" t="n">
-        <v>0.00740935996088564</v>
+        <v>-0.01193004232021133</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.03489758572708599</v>
+        <v>-0.1105412483358429</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.8697155083131587</v>
+        <v>0.01134630288189326</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.002406315815951078</v>
+        <v>-0.2660564792319032</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.008780674266115432</v>
+        <v>1.45737063857569</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.0002052034834714622</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.007409370087792433</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.01572714951544185</v>
+        <v>-0.1081508876107066</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.08683765283234379</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.1677748040038057</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.0005875320580061155</v>
+        <v>-13.42736196250189</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.6845186539110139</v>
+        <v>-94.94054335937926</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0.3473562317626602</v>
+        <v>-8.314361537792287</v>
       </c>
       <c r="AK32" t="n">
-        <v>-0.01572714951544185</v>
+        <v>-0.005102500778656233</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.08683765283234379</v>
+        <v>34.05107264136433</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.1677748040038057</v>
+        <v>-63.08419102967977</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.0005875320580061155</v>
+        <v>13.42736196250189</v>
       </c>
       <c r="AO32" t="n">
-        <v>-0.657679778119431</v>
+        <v>-105.0594566406207</v>
       </c>
       <c r="AP32" t="n">
-        <v>-0.347344990896147</v>
+        <v>8.314361537792287</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.005102500778656233</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>32.46381966097396</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>103.5598441546466</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>20</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>17</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>8</v>
       </c>
-      <c r="E33" t="n">
-        <v>-38.19320392980286</v>
-      </c>
       <c r="F33" t="n">
-        <v>-8057.63795987402</v>
+        <v>0.0006898370413459531</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8697155083131587</v>
+        <v>8.622963016824414e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>0.03489758572708599</v>
+        <v>81.74568939949545</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002406315815951078</v>
+        <v>17245.92603364883</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0002052034834714622</v>
+        <v>13.75040665788783</v>
       </c>
       <c r="K33" t="n">
-        <v>0.008780674266115432</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="L33" t="n">
-        <v>0.007409370087792433</v>
+        <v>-0.01708286628405483</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8693932027947637</v>
+        <v>0.009916345241901936</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.02354482424360938</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.002406814221431988</v>
+        <v>-0.3561669580448221</v>
       </c>
       <c r="P33" t="n">
-        <v>0.0001818926669167243</v>
+        <v>13.74971682084649</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.05018136607334805</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="R33" t="n">
-        <v>0.007409214359710549</v>
+        <v>0.01709782427089189</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8697155083131587</v>
+        <v>-0.009077683545820888</v>
       </c>
       <c r="T33" t="n">
-        <v>0.03489758572708599</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.002406315815951078</v>
+        <v>-0.2961131962401839</v>
       </c>
       <c r="V33" t="n">
-        <v>0.0002052034834714622</v>
+        <v>-13.75040665788783</v>
       </c>
       <c r="W33" t="n">
-        <v>0.008780674266115432</v>
+        <v>-1.45737063857569</v>
       </c>
       <c r="X33" t="n">
-        <v>-0.007409370087792433</v>
+        <v>0.01708286628405483</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.8693932027947637</v>
+        <v>-0.009916345241901936</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.02354482424360938</v>
+        <v>0.1081508876107066</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002406814221431988</v>
+        <v>0.3561669580448221</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.0001818926669167243</v>
+        <v>-13.74971682084649</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.05018136607334805</v>
+        <v>0.983163243548322</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.007409214359710549</v>
+        <v>-0.01709782427089189</v>
       </c>
       <c r="AE33" t="n">
-        <v>38.19320392979716</v>
+        <v>0.009077683545820888</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.0865724886976289</v>
+        <v>0.128253174079973</v>
       </c>
       <c r="AG33" t="n">
-        <v>16.7321716202454</v>
+        <v>0.2961131962401839</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.0008263013979440137</v>
+        <v>-81.74568939954042</v>
       </c>
       <c r="AI33" t="n">
-        <v>-34.20475409257939</v>
+        <v>17.54355711260374</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.3463763838759579</v>
+        <v>-94.84626256787126</v>
       </c>
       <c r="AK33" t="n">
-        <v>-38.19320392979716</v>
+        <v>-0.04054494606610064</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.0865724886976289</v>
+        <v>368.2282812810421</v>
       </c>
       <c r="AM33" t="n">
-        <v>-16.7321716202454</v>
+        <v>103.504066251989</v>
       </c>
       <c r="AN33" t="n">
-        <v>-0.0008263013979440137</v>
+        <v>81.74568939954042</v>
       </c>
       <c r="AO33" t="n">
-        <v>-99.65261886938386</v>
+        <v>-17.54355711260374</v>
       </c>
       <c r="AP33" t="n">
-        <v>-0.3462035257050662</v>
+        <v>94.84626256787126</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.04054494606610064</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>390.5418192619279</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>36.84439064884054</v>
       </c>
     </row>
   </sheetData>
